--- a/AAII_Financials/Yearly/TU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TU_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>TU</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>13298500</v>
+        <v>14783500</v>
       </c>
       <c r="E8" s="3">
-        <v>12241400</v>
+        <v>13517600</v>
       </c>
       <c r="F8" s="3">
-        <v>11153100</v>
+        <v>12443100</v>
       </c>
       <c r="G8" s="3">
-        <v>10606300</v>
+        <v>11336800</v>
       </c>
       <c r="H8" s="3">
-        <v>10247200</v>
+        <v>10781100</v>
       </c>
       <c r="I8" s="3">
-        <v>9672900</v>
+        <v>10416100</v>
       </c>
       <c r="J8" s="3">
+        <v>9832300</v>
+      </c>
+      <c r="K8" s="3">
         <v>9251200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9333200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9363300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8726700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8169300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7932000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5051300</v>
+        <v>5429400</v>
       </c>
       <c r="E9" s="3">
-        <v>4809900</v>
+        <v>5134500</v>
       </c>
       <c r="F9" s="3">
-        <v>4411500</v>
+        <v>4889200</v>
       </c>
       <c r="G9" s="3">
-        <v>4365700</v>
+        <v>4484200</v>
       </c>
       <c r="H9" s="3">
-        <v>4629600</v>
+        <v>4437600</v>
       </c>
       <c r="I9" s="3">
-        <v>4292300</v>
+        <v>4705900</v>
       </c>
       <c r="J9" s="3">
+        <v>4363000</v>
+      </c>
+      <c r="K9" s="3">
         <v>4093800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4153800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4160000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3819800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3628400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3630700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8247200</v>
+        <v>9354100</v>
       </c>
       <c r="E10" s="3">
-        <v>7431500</v>
+        <v>8383100</v>
       </c>
       <c r="F10" s="3">
-        <v>6741600</v>
+        <v>7554000</v>
       </c>
       <c r="G10" s="3">
-        <v>6240700</v>
+        <v>6852700</v>
       </c>
       <c r="H10" s="3">
-        <v>5617600</v>
+        <v>6343500</v>
       </c>
       <c r="I10" s="3">
-        <v>5380600</v>
+        <v>5710200</v>
       </c>
       <c r="J10" s="3">
+        <v>5469300</v>
+      </c>
+      <c r="K10" s="3">
         <v>5157400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5179400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5203300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4906800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4540800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4301300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,93 +960,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>174500</v>
+        <v>465600</v>
       </c>
       <c r="E14" s="3">
-        <v>135200</v>
+        <v>177400</v>
       </c>
       <c r="F14" s="3">
-        <v>151900</v>
+        <v>137500</v>
       </c>
       <c r="G14" s="3">
+        <v>154400</v>
+      </c>
+      <c r="H14" s="3">
+        <v>94600</v>
+      </c>
+      <c r="I14" s="3">
         <v>93100</v>
       </c>
-      <c r="H14" s="3">
-        <v>91600</v>
-      </c>
-      <c r="I14" s="3">
-        <v>18900</v>
-      </c>
       <c r="J14" s="3">
+        <v>19200</v>
+      </c>
+      <c r="K14" s="3">
         <v>81400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>117100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>42400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>54700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>28600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2509600</v>
+        <v>3007000</v>
       </c>
       <c r="E15" s="3">
-        <v>2338100</v>
+        <v>2551000</v>
       </c>
       <c r="F15" s="3">
-        <v>2189800</v>
+        <v>2376600</v>
       </c>
       <c r="G15" s="3">
-        <v>1873500</v>
+        <v>2225800</v>
       </c>
       <c r="H15" s="3">
-        <v>1648100</v>
+        <v>1904400</v>
       </c>
       <c r="I15" s="3">
-        <v>1576900</v>
+        <v>1675300</v>
       </c>
       <c r="J15" s="3">
+        <v>1602900</v>
+      </c>
+      <c r="K15" s="3">
         <v>1488200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1433400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1439800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1388000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1404000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1390500</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11150900</v>
+        <v>13038000</v>
       </c>
       <c r="E17" s="3">
-        <v>10006600</v>
+        <v>11334600</v>
       </c>
       <c r="F17" s="3">
-        <v>9348600</v>
+        <v>10171500</v>
       </c>
       <c r="G17" s="3">
-        <v>8442000</v>
+        <v>9502700</v>
       </c>
       <c r="H17" s="3">
-        <v>8184700</v>
+        <v>8581200</v>
       </c>
       <c r="I17" s="3">
-        <v>7680100</v>
+        <v>8319500</v>
       </c>
       <c r="J17" s="3">
+        <v>7806700</v>
+      </c>
+      <c r="K17" s="3">
         <v>7664900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7566400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7374800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7336400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6956500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6420100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2147600</v>
+        <v>1745500</v>
       </c>
       <c r="E18" s="3">
-        <v>2234800</v>
+        <v>2183000</v>
       </c>
       <c r="F18" s="3">
-        <v>1804400</v>
+        <v>2271700</v>
       </c>
       <c r="G18" s="3">
-        <v>2164300</v>
+        <v>1834200</v>
       </c>
       <c r="H18" s="3">
-        <v>2062500</v>
+        <v>2200000</v>
       </c>
       <c r="I18" s="3">
-        <v>1992700</v>
+        <v>2096500</v>
       </c>
       <c r="J18" s="3">
+        <v>2025600</v>
+      </c>
+      <c r="K18" s="3">
         <v>1586300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1766800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1988500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1390300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1212700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1511900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>150500</v>
+        <v>-12600</v>
       </c>
       <c r="E20" s="3">
-        <v>-25400</v>
+        <v>153000</v>
       </c>
       <c r="F20" s="3">
-        <v>-41400</v>
+        <v>-25900</v>
       </c>
       <c r="G20" s="3">
-        <v>-34200</v>
+        <v>-42100</v>
       </c>
       <c r="H20" s="3">
-        <v>-41400</v>
+        <v>-34700</v>
       </c>
       <c r="I20" s="3">
-        <v>-5100</v>
+        <v>-42100</v>
       </c>
       <c r="J20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-21800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-132700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>257100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>270300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6100</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4821800</v>
+        <v>4754000</v>
       </c>
       <c r="E21" s="3">
-        <v>4560600</v>
+        <v>4898900</v>
       </c>
       <c r="F21" s="3">
-        <v>3965100</v>
+        <v>4633500</v>
       </c>
       <c r="G21" s="3">
-        <v>4014200</v>
+        <v>4028300</v>
       </c>
       <c r="H21" s="3">
-        <v>3678500</v>
+        <v>4078500</v>
       </c>
       <c r="I21" s="3">
-        <v>3573400</v>
+        <v>3737500</v>
       </c>
       <c r="J21" s="3">
+        <v>3630800</v>
+      </c>
+      <c r="K21" s="3">
         <v>3061100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3186400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3290200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3032900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2887600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2915200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>610000</v>
+        <v>928200</v>
       </c>
       <c r="E22" s="3">
-        <v>553300</v>
+        <v>620000</v>
       </c>
       <c r="F22" s="3">
-        <v>519100</v>
+        <v>562400</v>
       </c>
       <c r="G22" s="3">
-        <v>498700</v>
+        <v>527600</v>
       </c>
       <c r="H22" s="3">
-        <v>439100</v>
+        <v>506900</v>
       </c>
       <c r="I22" s="3">
-        <v>411500</v>
+        <v>446300</v>
       </c>
       <c r="J22" s="3">
+        <v>418300</v>
+      </c>
+      <c r="K22" s="3">
         <v>356200</v>
-      </c>
-      <c r="K22" s="3">
-        <v>343900</v>
       </c>
       <c r="L22" s="3">
         <v>343900</v>
       </c>
       <c r="M22" s="3">
+        <v>343900</v>
+      </c>
+      <c r="N22" s="3">
         <v>286400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>263500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>295800</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1688100</v>
+        <v>804800</v>
       </c>
       <c r="E23" s="3">
-        <v>1656100</v>
+        <v>1715900</v>
       </c>
       <c r="F23" s="3">
-        <v>1243900</v>
+        <v>1683400</v>
       </c>
       <c r="G23" s="3">
-        <v>1631400</v>
+        <v>1264400</v>
       </c>
       <c r="H23" s="3">
-        <v>1582000</v>
+        <v>1658300</v>
       </c>
       <c r="I23" s="3">
-        <v>1576200</v>
+        <v>1608000</v>
       </c>
       <c r="J23" s="3">
+        <v>1602100</v>
+      </c>
+      <c r="K23" s="3">
         <v>1208300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1431100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1512000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1361000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1219500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1222300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>439100</v>
+        <v>164100</v>
       </c>
       <c r="E24" s="3">
-        <v>421700</v>
+        <v>446300</v>
       </c>
       <c r="F24" s="3">
-        <v>327900</v>
+        <v>428600</v>
       </c>
       <c r="G24" s="3">
-        <v>340200</v>
+        <v>333300</v>
       </c>
       <c r="H24" s="3">
-        <v>401300</v>
+        <v>345800</v>
       </c>
       <c r="I24" s="3">
-        <v>428900</v>
+        <v>407900</v>
       </c>
       <c r="J24" s="3">
+        <v>436000</v>
+      </c>
+      <c r="K24" s="3">
         <v>309700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>393500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>393300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>364900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>313200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>288900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1249000</v>
+        <v>640700</v>
       </c>
       <c r="E26" s="3">
-        <v>1234500</v>
+        <v>1269600</v>
       </c>
       <c r="F26" s="3">
-        <v>916000</v>
+        <v>1254800</v>
       </c>
       <c r="G26" s="3">
-        <v>1291200</v>
+        <v>931100</v>
       </c>
       <c r="H26" s="3">
-        <v>1180700</v>
+        <v>1312400</v>
       </c>
       <c r="I26" s="3">
-        <v>1147200</v>
+        <v>1200100</v>
       </c>
       <c r="J26" s="3">
+        <v>1166100</v>
+      </c>
+      <c r="K26" s="3">
         <v>898600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1037700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1118700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>996100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>906400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>933400</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1174100</v>
+        <v>621500</v>
       </c>
       <c r="E27" s="3">
-        <v>1203200</v>
+        <v>1193500</v>
       </c>
       <c r="F27" s="3">
-        <v>877500</v>
+        <v>1223000</v>
       </c>
       <c r="G27" s="3">
-        <v>1269400</v>
+        <v>892000</v>
       </c>
       <c r="H27" s="3">
-        <v>1163200</v>
+        <v>1290300</v>
       </c>
       <c r="I27" s="3">
-        <v>1133400</v>
+        <v>1182400</v>
       </c>
       <c r="J27" s="3">
+        <v>1152100</v>
+      </c>
+      <c r="K27" s="3">
         <v>889100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1037700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1118700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>996100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>906400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>936500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-150500</v>
+        <v>12600</v>
       </c>
       <c r="E32" s="3">
-        <v>25400</v>
+        <v>-153000</v>
       </c>
       <c r="F32" s="3">
-        <v>41400</v>
+        <v>25900</v>
       </c>
       <c r="G32" s="3">
-        <v>34200</v>
+        <v>42100</v>
       </c>
       <c r="H32" s="3">
-        <v>41400</v>
+        <v>34700</v>
       </c>
       <c r="I32" s="3">
-        <v>5100</v>
+        <v>42100</v>
       </c>
       <c r="J32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K32" s="3">
         <v>21800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>132700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-257100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-270300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6100</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1174100</v>
+        <v>621500</v>
       </c>
       <c r="E33" s="3">
-        <v>1203200</v>
+        <v>1193500</v>
       </c>
       <c r="F33" s="3">
-        <v>877500</v>
+        <v>1223000</v>
       </c>
       <c r="G33" s="3">
-        <v>1269400</v>
+        <v>892000</v>
       </c>
       <c r="H33" s="3">
-        <v>1163200</v>
+        <v>1290300</v>
       </c>
       <c r="I33" s="3">
-        <v>1133400</v>
+        <v>1182400</v>
       </c>
       <c r="J33" s="3">
+        <v>1152100</v>
+      </c>
+      <c r="K33" s="3">
         <v>889100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1037700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1118700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>996100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>906400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>936500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1174100</v>
+        <v>621500</v>
       </c>
       <c r="E35" s="3">
-        <v>1203200</v>
+        <v>1193500</v>
       </c>
       <c r="F35" s="3">
-        <v>877500</v>
+        <v>1223000</v>
       </c>
       <c r="G35" s="3">
-        <v>1269400</v>
+        <v>892000</v>
       </c>
       <c r="H35" s="3">
-        <v>1163200</v>
+        <v>1290300</v>
       </c>
       <c r="I35" s="3">
-        <v>1133400</v>
+        <v>1182400</v>
       </c>
       <c r="J35" s="3">
+        <v>1152100</v>
+      </c>
+      <c r="K35" s="3">
         <v>889100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1037700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1118700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>996100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>906400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>936500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1986,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>708100</v>
+        <v>638500</v>
       </c>
       <c r="E41" s="3">
-        <v>525600</v>
+        <v>719800</v>
       </c>
       <c r="F41" s="3">
-        <v>616500</v>
+        <v>534300</v>
       </c>
       <c r="G41" s="3">
-        <v>389000</v>
+        <v>626700</v>
       </c>
       <c r="H41" s="3">
-        <v>301000</v>
+        <v>395400</v>
       </c>
       <c r="I41" s="3">
-        <v>370000</v>
+        <v>305900</v>
       </c>
       <c r="J41" s="3">
+        <v>376100</v>
+      </c>
+      <c r="K41" s="3">
         <v>314100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>167400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>47100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>258700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>80500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>35300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,303 +2073,327 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2821500</v>
+        <v>3138500</v>
       </c>
       <c r="E43" s="3">
-        <v>2413700</v>
+        <v>2868000</v>
       </c>
       <c r="F43" s="3">
-        <v>2138900</v>
+        <v>2453400</v>
       </c>
       <c r="G43" s="3">
-        <v>2054500</v>
+        <v>2174100</v>
       </c>
       <c r="H43" s="3">
-        <v>1790600</v>
+        <v>2088400</v>
       </c>
       <c r="I43" s="3">
-        <v>1793500</v>
+        <v>1820100</v>
       </c>
       <c r="J43" s="3">
+        <v>1823100</v>
+      </c>
+      <c r="K43" s="3">
         <v>1076000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1073000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1240400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1149300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1178900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1147700</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>390400</v>
+        <v>357700</v>
       </c>
       <c r="E44" s="3">
-        <v>325700</v>
+        <v>396800</v>
       </c>
       <c r="F44" s="3">
-        <v>295900</v>
+        <v>331100</v>
       </c>
       <c r="G44" s="3">
-        <v>317700</v>
+        <v>300800</v>
       </c>
       <c r="H44" s="3">
-        <v>273400</v>
+        <v>322900</v>
       </c>
       <c r="I44" s="3">
-        <v>276300</v>
+        <v>277900</v>
       </c>
       <c r="J44" s="3">
+        <v>280800</v>
+      </c>
+      <c r="K44" s="3">
         <v>231200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>270300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>251200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>251000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>263500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>271200</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>508900</v>
+        <v>530600</v>
       </c>
       <c r="E45" s="3">
-        <v>393300</v>
+        <v>517300</v>
       </c>
       <c r="F45" s="3">
-        <v>349000</v>
+        <v>399800</v>
       </c>
       <c r="G45" s="3">
-        <v>403500</v>
+        <v>354700</v>
       </c>
       <c r="H45" s="3">
-        <v>427500</v>
+        <v>410100</v>
       </c>
       <c r="I45" s="3">
-        <v>371500</v>
+        <v>434500</v>
       </c>
       <c r="J45" s="3">
+        <v>377600</v>
+      </c>
+      <c r="K45" s="3">
         <v>177400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>239500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>177400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>133900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>140800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>121400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4428900</v>
+        <v>4665200</v>
       </c>
       <c r="E46" s="3">
-        <v>3658300</v>
+        <v>4501900</v>
       </c>
       <c r="F46" s="3">
-        <v>3400200</v>
+        <v>3718600</v>
       </c>
       <c r="G46" s="3">
-        <v>3164700</v>
+        <v>3456300</v>
       </c>
       <c r="H46" s="3">
-        <v>2792400</v>
+        <v>3216800</v>
       </c>
       <c r="I46" s="3">
-        <v>2811300</v>
+        <v>2838500</v>
       </c>
       <c r="J46" s="3">
+        <v>2857700</v>
+      </c>
+      <c r="K46" s="3">
         <v>1798600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1750300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1716100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1792900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1663700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1575600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1173400</v>
+        <v>1374500</v>
       </c>
       <c r="E47" s="3">
-        <v>1100000</v>
+        <v>1192700</v>
       </c>
       <c r="F47" s="3">
-        <v>762600</v>
+        <v>1118100</v>
       </c>
       <c r="G47" s="3">
-        <v>396200</v>
+        <v>775200</v>
       </c>
       <c r="H47" s="3">
-        <v>437700</v>
+        <v>402700</v>
       </c>
       <c r="I47" s="3">
-        <v>351900</v>
+        <v>444900</v>
       </c>
       <c r="J47" s="3">
+        <v>357700</v>
+      </c>
+      <c r="K47" s="3">
         <v>60300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>70600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>55000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>43700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12420200</v>
+        <v>12746100</v>
       </c>
       <c r="E48" s="3">
-        <v>11578400</v>
+        <v>12624900</v>
       </c>
       <c r="F48" s="3">
-        <v>10915300</v>
+        <v>11769200</v>
       </c>
       <c r="G48" s="3">
-        <v>10346800</v>
+        <v>11095200</v>
       </c>
       <c r="H48" s="3">
-        <v>8790300</v>
+        <v>10517300</v>
       </c>
       <c r="I48" s="3">
-        <v>8264600</v>
+        <v>8935100</v>
       </c>
       <c r="J48" s="3">
+        <v>8400800</v>
+      </c>
+      <c r="K48" s="3">
         <v>7607400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7310400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7162000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6486500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6146500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6118200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>20608600</v>
+        <v>22006400</v>
       </c>
       <c r="E49" s="3">
-        <v>18005100</v>
+        <v>20948100</v>
       </c>
       <c r="F49" s="3">
-        <v>16145400</v>
+        <v>18301800</v>
       </c>
       <c r="G49" s="3">
-        <v>13197400</v>
+        <v>16411500</v>
       </c>
       <c r="H49" s="3">
-        <v>11400200</v>
+        <v>13414900</v>
       </c>
       <c r="I49" s="3">
-        <v>10828100</v>
+        <v>11588100</v>
       </c>
       <c r="J49" s="3">
+        <v>11006500</v>
+      </c>
+      <c r="K49" s="3">
         <v>10287900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10321300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9070500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7904500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7439800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7539400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>660900</v>
+        <v>691700</v>
       </c>
       <c r="E52" s="3">
-        <v>550300</v>
+        <v>671700</v>
       </c>
       <c r="F52" s="3">
-        <v>236300</v>
+        <v>559400</v>
       </c>
       <c r="G52" s="3">
-        <v>510400</v>
+        <v>240200</v>
       </c>
       <c r="H52" s="3">
-        <v>612100</v>
+        <v>518800</v>
       </c>
       <c r="I52" s="3">
-        <v>319900</v>
+        <v>622200</v>
       </c>
       <c r="J52" s="3">
+        <v>325200</v>
+      </c>
+      <c r="K52" s="3">
         <v>404900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>374700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>223000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>371100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>97100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>39292000</v>
+        <v>41483900</v>
       </c>
       <c r="E54" s="3">
-        <v>34892100</v>
+        <v>39939500</v>
       </c>
       <c r="F54" s="3">
-        <v>31459900</v>
+        <v>35467100</v>
       </c>
       <c r="G54" s="3">
-        <v>27615500</v>
+        <v>31978300</v>
       </c>
       <c r="H54" s="3">
-        <v>24032800</v>
+        <v>28070500</v>
       </c>
       <c r="I54" s="3">
-        <v>22575800</v>
+        <v>24428800</v>
       </c>
       <c r="J54" s="3">
+        <v>22947900</v>
+      </c>
+      <c r="K54" s="3">
         <v>20159300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19827200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18226500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16600400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15390800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15311600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1004700</v>
+        <v>736000</v>
       </c>
       <c r="E57" s="3">
-        <v>881900</v>
+        <v>1021300</v>
       </c>
       <c r="F57" s="3">
-        <v>628100</v>
+        <v>896400</v>
       </c>
       <c r="G57" s="3">
-        <v>648500</v>
+        <v>638500</v>
       </c>
       <c r="H57" s="3">
-        <v>498700</v>
+        <v>659200</v>
       </c>
       <c r="I57" s="3">
-        <v>521300</v>
+        <v>506900</v>
       </c>
       <c r="J57" s="3">
+        <v>529900</v>
+      </c>
+      <c r="K57" s="3">
         <v>420200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>357400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>359600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>352600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>353100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>348000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1922900</v>
+        <v>3028400</v>
       </c>
       <c r="E58" s="3">
-        <v>2210800</v>
+        <v>1954600</v>
       </c>
       <c r="F58" s="3">
-        <v>1113800</v>
+        <v>2247300</v>
       </c>
       <c r="G58" s="3">
-        <v>1041100</v>
+        <v>1132100</v>
       </c>
       <c r="H58" s="3">
-        <v>680500</v>
+        <v>1058200</v>
       </c>
       <c r="I58" s="3">
-        <v>1093400</v>
+        <v>691700</v>
       </c>
       <c r="J58" s="3">
+        <v>1111400</v>
+      </c>
+      <c r="K58" s="3">
         <v>1037400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>717800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>278700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>307900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>712900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1129300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3092700</v>
+        <v>3239700</v>
       </c>
       <c r="E59" s="3">
-        <v>2921900</v>
+        <v>3143700</v>
       </c>
       <c r="F59" s="3">
-        <v>2551100</v>
+        <v>2970000</v>
       </c>
       <c r="G59" s="3">
-        <v>2759000</v>
+        <v>2593100</v>
       </c>
       <c r="H59" s="3">
-        <v>2817200</v>
+        <v>2804500</v>
       </c>
       <c r="I59" s="3">
-        <v>2049400</v>
+        <v>2863600</v>
       </c>
       <c r="J59" s="3">
+        <v>2083200</v>
+      </c>
+      <c r="K59" s="3">
         <v>2141800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2135400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2108600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1879100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1583900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1476500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6020400</v>
+        <v>7004100</v>
       </c>
       <c r="E60" s="3">
-        <v>6014600</v>
+        <v>6119600</v>
       </c>
       <c r="F60" s="3">
-        <v>4293000</v>
+        <v>6113700</v>
       </c>
       <c r="G60" s="3">
-        <v>4052400</v>
+        <v>4363700</v>
       </c>
       <c r="H60" s="3">
-        <v>3521600</v>
+        <v>4119100</v>
       </c>
       <c r="I60" s="3">
-        <v>3664100</v>
+        <v>3579700</v>
       </c>
       <c r="J60" s="3">
+        <v>3724500</v>
+      </c>
+      <c r="K60" s="3">
         <v>3599400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3210700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2746900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2539600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2649800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2953800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16354800</v>
+        <v>17259100</v>
       </c>
       <c r="E61" s="3">
-        <v>13031700</v>
+        <v>16624300</v>
       </c>
       <c r="F61" s="3">
-        <v>13708500</v>
+        <v>13246400</v>
       </c>
       <c r="G61" s="3">
-        <v>12462400</v>
+        <v>13934400</v>
       </c>
       <c r="H61" s="3">
-        <v>9643800</v>
+        <v>12667800</v>
       </c>
       <c r="I61" s="3">
-        <v>8910200</v>
+        <v>9802700</v>
       </c>
       <c r="J61" s="3">
+        <v>9057100</v>
+      </c>
+      <c r="K61" s="3">
         <v>8436200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8396100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7108600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5768300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4299200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4231400</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4079300</v>
+        <v>4434700</v>
       </c>
       <c r="E62" s="3">
-        <v>4170900</v>
+        <v>4146500</v>
       </c>
       <c r="F62" s="3">
-        <v>4993100</v>
+        <v>4239600</v>
       </c>
       <c r="G62" s="3">
-        <v>3407500</v>
+        <v>5075400</v>
       </c>
       <c r="H62" s="3">
-        <v>3940400</v>
+        <v>3463600</v>
       </c>
       <c r="I62" s="3">
-        <v>3125400</v>
+        <v>4005300</v>
       </c>
       <c r="J62" s="3">
+        <v>3176900</v>
+      </c>
+      <c r="K62" s="3">
         <v>2354100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2459800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2519200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2123900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2655800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2354600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27246200</v>
+        <v>29577300</v>
       </c>
       <c r="E66" s="3">
-        <v>23902600</v>
+        <v>27695100</v>
       </c>
       <c r="F66" s="3">
-        <v>22706700</v>
+        <v>24296500</v>
       </c>
       <c r="G66" s="3">
-        <v>19947000</v>
+        <v>23080900</v>
       </c>
       <c r="H66" s="3">
-        <v>16574400</v>
+        <v>20275700</v>
       </c>
       <c r="I66" s="3">
-        <v>15730300</v>
+        <v>16847500</v>
       </c>
       <c r="J66" s="3">
+        <v>15989500</v>
+      </c>
+      <c r="K66" s="3">
         <v>14403500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14066600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12374700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10431800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9604800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9539900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2983600</v>
+        <v>2095000</v>
       </c>
       <c r="E72" s="3">
-        <v>3094200</v>
+        <v>3032800</v>
       </c>
       <c r="F72" s="3">
-        <v>2698700</v>
+        <v>3145100</v>
       </c>
       <c r="G72" s="3">
-        <v>3177800</v>
+        <v>2743100</v>
       </c>
       <c r="H72" s="3">
-        <v>3252600</v>
+        <v>3230100</v>
       </c>
       <c r="I72" s="3">
-        <v>2758300</v>
+        <v>3306200</v>
       </c>
       <c r="J72" s="3">
+        <v>2803700</v>
+      </c>
+      <c r="K72" s="3">
         <v>1798600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1823100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1648600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1954600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1433300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1367400</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12045800</v>
+        <v>11906600</v>
       </c>
       <c r="E76" s="3">
-        <v>10989500</v>
+        <v>12244300</v>
       </c>
       <c r="F76" s="3">
-        <v>8753200</v>
+        <v>11170600</v>
       </c>
       <c r="G76" s="3">
-        <v>7668500</v>
+        <v>8897400</v>
       </c>
       <c r="H76" s="3">
-        <v>7458400</v>
+        <v>7794900</v>
       </c>
       <c r="I76" s="3">
-        <v>6845500</v>
+        <v>7581300</v>
       </c>
       <c r="J76" s="3">
+        <v>6958300</v>
+      </c>
+      <c r="K76" s="3">
         <v>5755700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5760600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5851800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6170100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5785900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5771700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1174100</v>
+        <v>621500</v>
       </c>
       <c r="E81" s="3">
-        <v>1203200</v>
+        <v>1193500</v>
       </c>
       <c r="F81" s="3">
-        <v>877500</v>
+        <v>1223000</v>
       </c>
       <c r="G81" s="3">
-        <v>1269400</v>
+        <v>892000</v>
       </c>
       <c r="H81" s="3">
-        <v>1163200</v>
+        <v>1290300</v>
       </c>
       <c r="I81" s="3">
-        <v>1133400</v>
+        <v>1182400</v>
       </c>
       <c r="J81" s="3">
+        <v>1152100</v>
+      </c>
+      <c r="K81" s="3">
         <v>889100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1037700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1118700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>996100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>906400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>936500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2509600</v>
+        <v>3007000</v>
       </c>
       <c r="E83" s="3">
-        <v>2338100</v>
+        <v>2551000</v>
       </c>
       <c r="F83" s="3">
-        <v>2189800</v>
+        <v>2376600</v>
       </c>
       <c r="G83" s="3">
-        <v>1873500</v>
+        <v>2225800</v>
       </c>
       <c r="H83" s="3">
-        <v>1648100</v>
+        <v>1904400</v>
       </c>
       <c r="I83" s="3">
-        <v>1576900</v>
+        <v>1675300</v>
       </c>
       <c r="J83" s="3">
+        <v>1602900</v>
+      </c>
+      <c r="K83" s="3">
         <v>1488200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1433400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1439800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1388000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1404000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1390500</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3497600</v>
+        <v>3324700</v>
       </c>
       <c r="E89" s="3">
-        <v>3190100</v>
+        <v>3555300</v>
       </c>
       <c r="F89" s="3">
-        <v>3325300</v>
+        <v>3242700</v>
       </c>
       <c r="G89" s="3">
-        <v>2855000</v>
+        <v>3380100</v>
       </c>
       <c r="H89" s="3">
-        <v>2950200</v>
+        <v>2902000</v>
       </c>
       <c r="I89" s="3">
-        <v>2869500</v>
+        <v>2998800</v>
       </c>
       <c r="J89" s="3">
+        <v>2916800</v>
+      </c>
+      <c r="K89" s="3">
         <v>2340200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2670100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2674700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2498800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2423200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1959000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2392600</v>
+        <v>-1937600</v>
       </c>
       <c r="E91" s="3">
-        <v>-2317700</v>
+        <v>-2432000</v>
       </c>
       <c r="F91" s="3">
-        <v>-1942600</v>
+        <v>-2355900</v>
       </c>
       <c r="G91" s="3">
-        <v>-2015300</v>
+        <v>-1974600</v>
       </c>
       <c r="H91" s="3">
-        <v>-1732500</v>
+        <v>-2048500</v>
       </c>
       <c r="I91" s="3">
-        <v>-1807300</v>
+        <v>-1761000</v>
       </c>
       <c r="J91" s="3">
+        <v>-1837100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1714300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1536300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1505700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1266400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2644600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1418900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3931700</v>
+        <v>-3508700</v>
       </c>
       <c r="E94" s="3">
-        <v>-3973800</v>
+        <v>-3996500</v>
       </c>
       <c r="F94" s="3">
-        <v>-4482000</v>
+        <v>-4039300</v>
       </c>
       <c r="G94" s="3">
-        <v>-3667000</v>
+        <v>-4555900</v>
       </c>
       <c r="H94" s="3">
-        <v>-2164300</v>
+        <v>-3727500</v>
       </c>
       <c r="I94" s="3">
-        <v>-2648500</v>
+        <v>-2200000</v>
       </c>
       <c r="J94" s="3">
+        <v>-2692100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2125100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3361600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2879600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1839100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1549200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1511900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-863700</v>
+        <v>-971800</v>
       </c>
       <c r="E96" s="3">
-        <v>-759700</v>
+        <v>-877900</v>
       </c>
       <c r="F96" s="3">
-        <v>-676100</v>
+        <v>-772200</v>
       </c>
       <c r="G96" s="3">
-        <v>-835300</v>
+        <v>-687300</v>
       </c>
       <c r="H96" s="3">
-        <v>-829500</v>
+        <v>-849100</v>
       </c>
       <c r="I96" s="3">
-        <v>-786600</v>
+        <v>-843200</v>
       </c>
       <c r="J96" s="3">
+        <v>-799600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-777900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-744900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-716800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-655900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-582700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-493200</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4397,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>616500</v>
+        <v>102700</v>
       </c>
       <c r="E100" s="3">
-        <v>692800</v>
+        <v>626700</v>
       </c>
       <c r="F100" s="3">
-        <v>1384200</v>
+        <v>704300</v>
       </c>
       <c r="G100" s="3">
-        <v>900000</v>
+        <v>1407000</v>
       </c>
       <c r="H100" s="3">
-        <v>-855000</v>
+        <v>914900</v>
       </c>
       <c r="I100" s="3">
-        <v>-165000</v>
+        <v>-869100</v>
       </c>
       <c r="J100" s="3">
+        <v>-167800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-63200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>813900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-483400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-828100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-424800</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4239,49 +4487,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>182500</v>
+        <v>-81300</v>
       </c>
       <c r="E102" s="3">
-        <v>-90900</v>
+        <v>185500</v>
       </c>
       <c r="F102" s="3">
-        <v>227600</v>
+        <v>-92400</v>
       </c>
       <c r="G102" s="3">
-        <v>88000</v>
+        <v>231300</v>
       </c>
       <c r="H102" s="3">
-        <v>-69100</v>
+        <v>89400</v>
       </c>
       <c r="I102" s="3">
-        <v>56000</v>
+        <v>-70200</v>
       </c>
       <c r="J102" s="3">
+        <v>56900</v>
+      </c>
+      <c r="K102" s="3">
         <v>151900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>122400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-216700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>176300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>45900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>22300</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TU_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14783500</v>
+        <v>14578800</v>
       </c>
       <c r="E8" s="3">
-        <v>13517600</v>
+        <v>13330500</v>
       </c>
       <c r="F8" s="3">
-        <v>12443100</v>
+        <v>12270900</v>
       </c>
       <c r="G8" s="3">
-        <v>11336800</v>
+        <v>11179900</v>
       </c>
       <c r="H8" s="3">
-        <v>10781100</v>
+        <v>10631900</v>
       </c>
       <c r="I8" s="3">
-        <v>10416100</v>
+        <v>10271900</v>
       </c>
       <c r="J8" s="3">
-        <v>9832300</v>
+        <v>9696200</v>
       </c>
       <c r="K8" s="3">
         <v>9251200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5429400</v>
+        <v>5354200</v>
       </c>
       <c r="E9" s="3">
-        <v>5134500</v>
+        <v>5063400</v>
       </c>
       <c r="F9" s="3">
-        <v>4889200</v>
+        <v>4821500</v>
       </c>
       <c r="G9" s="3">
-        <v>4484200</v>
+        <v>4422100</v>
       </c>
       <c r="H9" s="3">
-        <v>4437600</v>
+        <v>4376200</v>
       </c>
       <c r="I9" s="3">
-        <v>4705900</v>
+        <v>4640700</v>
       </c>
       <c r="J9" s="3">
-        <v>4363000</v>
+        <v>4302600</v>
       </c>
       <c r="K9" s="3">
         <v>4093800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9354100</v>
+        <v>9224600</v>
       </c>
       <c r="E10" s="3">
-        <v>8383100</v>
+        <v>8267100</v>
       </c>
       <c r="F10" s="3">
-        <v>7554000</v>
+        <v>7449400</v>
       </c>
       <c r="G10" s="3">
-        <v>6852700</v>
+        <v>6757800</v>
       </c>
       <c r="H10" s="3">
-        <v>6343500</v>
+        <v>6255700</v>
       </c>
       <c r="I10" s="3">
-        <v>5710200</v>
+        <v>5631100</v>
       </c>
       <c r="J10" s="3">
-        <v>5469300</v>
+        <v>5393600</v>
       </c>
       <c r="K10" s="3">
         <v>5157400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>465600</v>
+        <v>459100</v>
       </c>
       <c r="E14" s="3">
-        <v>177400</v>
+        <v>174900</v>
       </c>
       <c r="F14" s="3">
-        <v>137500</v>
+        <v>135500</v>
       </c>
       <c r="G14" s="3">
-        <v>154400</v>
+        <v>152300</v>
       </c>
       <c r="H14" s="3">
-        <v>94600</v>
+        <v>93300</v>
       </c>
       <c r="I14" s="3">
-        <v>93100</v>
+        <v>91800</v>
       </c>
       <c r="J14" s="3">
-        <v>19200</v>
+        <v>18900</v>
       </c>
       <c r="K14" s="3">
         <v>81400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3007000</v>
+        <v>2965300</v>
       </c>
       <c r="E15" s="3">
-        <v>2551000</v>
+        <v>2515700</v>
       </c>
       <c r="F15" s="3">
-        <v>2376600</v>
+        <v>2343700</v>
       </c>
       <c r="G15" s="3">
-        <v>2225800</v>
+        <v>2195000</v>
       </c>
       <c r="H15" s="3">
-        <v>1904400</v>
+        <v>1878000</v>
       </c>
       <c r="I15" s="3">
-        <v>1675300</v>
+        <v>1652100</v>
       </c>
       <c r="J15" s="3">
-        <v>1602900</v>
+        <v>1580700</v>
       </c>
       <c r="K15" s="3">
         <v>1488200</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13038000</v>
+        <v>12857500</v>
       </c>
       <c r="E17" s="3">
-        <v>11334600</v>
+        <v>11177700</v>
       </c>
       <c r="F17" s="3">
-        <v>10171500</v>
+        <v>10030700</v>
       </c>
       <c r="G17" s="3">
-        <v>9502700</v>
+        <v>9371100</v>
       </c>
       <c r="H17" s="3">
-        <v>8581200</v>
+        <v>8462400</v>
       </c>
       <c r="I17" s="3">
-        <v>8319500</v>
+        <v>8204400</v>
       </c>
       <c r="J17" s="3">
-        <v>7806700</v>
+        <v>7698600</v>
       </c>
       <c r="K17" s="3">
         <v>7664900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1745500</v>
+        <v>1721300</v>
       </c>
       <c r="E18" s="3">
-        <v>2183000</v>
+        <v>2152800</v>
       </c>
       <c r="F18" s="3">
-        <v>2271700</v>
+        <v>2240200</v>
       </c>
       <c r="G18" s="3">
-        <v>1834200</v>
+        <v>1808800</v>
       </c>
       <c r="H18" s="3">
-        <v>2200000</v>
+        <v>2169500</v>
       </c>
       <c r="I18" s="3">
-        <v>2096500</v>
+        <v>2067500</v>
       </c>
       <c r="J18" s="3">
-        <v>2025600</v>
+        <v>1997500</v>
       </c>
       <c r="K18" s="3">
         <v>1586300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-12600</v>
+        <v>-12400</v>
       </c>
       <c r="E20" s="3">
-        <v>153000</v>
+        <v>150900</v>
       </c>
       <c r="F20" s="3">
-        <v>-25900</v>
+        <v>-25500</v>
       </c>
       <c r="G20" s="3">
-        <v>-42100</v>
+        <v>-41500</v>
       </c>
       <c r="H20" s="3">
-        <v>-34700</v>
+        <v>-34300</v>
       </c>
       <c r="I20" s="3">
-        <v>-42100</v>
+        <v>-41500</v>
       </c>
       <c r="J20" s="3">
-        <v>-5200</v>
+        <v>-5100</v>
       </c>
       <c r="K20" s="3">
         <v>-21800</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4754000</v>
+        <v>4666700</v>
       </c>
       <c r="E21" s="3">
-        <v>4898900</v>
+        <v>4812900</v>
       </c>
       <c r="F21" s="3">
-        <v>4633500</v>
+        <v>4552400</v>
       </c>
       <c r="G21" s="3">
-        <v>4028300</v>
+        <v>3956700</v>
       </c>
       <c r="H21" s="3">
-        <v>4078500</v>
+        <v>4008500</v>
       </c>
       <c r="I21" s="3">
-        <v>3737500</v>
+        <v>3673800</v>
       </c>
       <c r="J21" s="3">
-        <v>3630800</v>
+        <v>3569100</v>
       </c>
       <c r="K21" s="3">
         <v>3061100</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>928200</v>
+        <v>915300</v>
       </c>
       <c r="E22" s="3">
-        <v>620000</v>
+        <v>611400</v>
       </c>
       <c r="F22" s="3">
-        <v>562400</v>
+        <v>554600</v>
       </c>
       <c r="G22" s="3">
-        <v>527600</v>
+        <v>520300</v>
       </c>
       <c r="H22" s="3">
-        <v>506900</v>
+        <v>499900</v>
       </c>
       <c r="I22" s="3">
-        <v>446300</v>
+        <v>440200</v>
       </c>
       <c r="J22" s="3">
-        <v>418300</v>
+        <v>412500</v>
       </c>
       <c r="K22" s="3">
         <v>356200</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>804800</v>
+        <v>793600</v>
       </c>
       <c r="E23" s="3">
-        <v>1715900</v>
+        <v>1692200</v>
       </c>
       <c r="F23" s="3">
-        <v>1683400</v>
+        <v>1660100</v>
       </c>
       <c r="G23" s="3">
-        <v>1264400</v>
+        <v>1246900</v>
       </c>
       <c r="H23" s="3">
-        <v>1658300</v>
+        <v>1635300</v>
       </c>
       <c r="I23" s="3">
-        <v>1608000</v>
+        <v>1585800</v>
       </c>
       <c r="J23" s="3">
-        <v>1602100</v>
+        <v>1580000</v>
       </c>
       <c r="K23" s="3">
         <v>1208300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>164100</v>
+        <v>161800</v>
       </c>
       <c r="E24" s="3">
-        <v>446300</v>
+        <v>440200</v>
       </c>
       <c r="F24" s="3">
-        <v>428600</v>
+        <v>422700</v>
       </c>
       <c r="G24" s="3">
-        <v>333300</v>
+        <v>328700</v>
       </c>
       <c r="H24" s="3">
-        <v>345800</v>
+        <v>341100</v>
       </c>
       <c r="I24" s="3">
-        <v>407900</v>
+        <v>402300</v>
       </c>
       <c r="J24" s="3">
-        <v>436000</v>
+        <v>430000</v>
       </c>
       <c r="K24" s="3">
         <v>309700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>640700</v>
+        <v>631800</v>
       </c>
       <c r="E26" s="3">
-        <v>1269600</v>
+        <v>1252000</v>
       </c>
       <c r="F26" s="3">
-        <v>1254800</v>
+        <v>1237400</v>
       </c>
       <c r="G26" s="3">
-        <v>931100</v>
+        <v>918200</v>
       </c>
       <c r="H26" s="3">
-        <v>1312400</v>
+        <v>1294300</v>
       </c>
       <c r="I26" s="3">
-        <v>1200100</v>
+        <v>1183500</v>
       </c>
       <c r="J26" s="3">
-        <v>1166100</v>
+        <v>1150000</v>
       </c>
       <c r="K26" s="3">
         <v>898600</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>621500</v>
+        <v>612900</v>
       </c>
       <c r="E27" s="3">
-        <v>1193500</v>
+        <v>1176900</v>
       </c>
       <c r="F27" s="3">
-        <v>1223000</v>
+        <v>1206100</v>
       </c>
       <c r="G27" s="3">
-        <v>892000</v>
+        <v>879600</v>
       </c>
       <c r="H27" s="3">
-        <v>1290300</v>
+        <v>1272400</v>
       </c>
       <c r="I27" s="3">
-        <v>1182400</v>
+        <v>1166000</v>
       </c>
       <c r="J27" s="3">
-        <v>1152100</v>
+        <v>1136100</v>
       </c>
       <c r="K27" s="3">
         <v>889100</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>12600</v>
+        <v>12400</v>
       </c>
       <c r="E32" s="3">
-        <v>-153000</v>
+        <v>-150900</v>
       </c>
       <c r="F32" s="3">
-        <v>25900</v>
+        <v>25500</v>
       </c>
       <c r="G32" s="3">
-        <v>42100</v>
+        <v>41500</v>
       </c>
       <c r="H32" s="3">
-        <v>34700</v>
+        <v>34300</v>
       </c>
       <c r="I32" s="3">
-        <v>42100</v>
+        <v>41500</v>
       </c>
       <c r="J32" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="K32" s="3">
         <v>21800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>621500</v>
+        <v>612900</v>
       </c>
       <c r="E33" s="3">
-        <v>1193500</v>
+        <v>1176900</v>
       </c>
       <c r="F33" s="3">
-        <v>1223000</v>
+        <v>1206100</v>
       </c>
       <c r="G33" s="3">
-        <v>892000</v>
+        <v>879600</v>
       </c>
       <c r="H33" s="3">
-        <v>1290300</v>
+        <v>1272400</v>
       </c>
       <c r="I33" s="3">
-        <v>1182400</v>
+        <v>1166000</v>
       </c>
       <c r="J33" s="3">
-        <v>1152100</v>
+        <v>1136100</v>
       </c>
       <c r="K33" s="3">
         <v>889100</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>621500</v>
+        <v>612900</v>
       </c>
       <c r="E35" s="3">
-        <v>1193500</v>
+        <v>1176900</v>
       </c>
       <c r="F35" s="3">
-        <v>1223000</v>
+        <v>1206100</v>
       </c>
       <c r="G35" s="3">
-        <v>892000</v>
+        <v>879600</v>
       </c>
       <c r="H35" s="3">
-        <v>1290300</v>
+        <v>1272400</v>
       </c>
       <c r="I35" s="3">
-        <v>1182400</v>
+        <v>1166000</v>
       </c>
       <c r="J35" s="3">
-        <v>1152100</v>
+        <v>1136100</v>
       </c>
       <c r="K35" s="3">
         <v>889100</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>638500</v>
+        <v>629600</v>
       </c>
       <c r="E41" s="3">
-        <v>719800</v>
+        <v>709800</v>
       </c>
       <c r="F41" s="3">
-        <v>534300</v>
+        <v>526900</v>
       </c>
       <c r="G41" s="3">
-        <v>626700</v>
+        <v>618000</v>
       </c>
       <c r="H41" s="3">
-        <v>395400</v>
+        <v>389900</v>
       </c>
       <c r="I41" s="3">
-        <v>305900</v>
+        <v>301700</v>
       </c>
       <c r="J41" s="3">
-        <v>376100</v>
+        <v>370900</v>
       </c>
       <c r="K41" s="3">
         <v>314100</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3138500</v>
+        <v>3095000</v>
       </c>
       <c r="E43" s="3">
-        <v>2868000</v>
+        <v>2828300</v>
       </c>
       <c r="F43" s="3">
-        <v>2453400</v>
+        <v>2419500</v>
       </c>
       <c r="G43" s="3">
-        <v>2174100</v>
+        <v>2144000</v>
       </c>
       <c r="H43" s="3">
-        <v>2088400</v>
+        <v>2059500</v>
       </c>
       <c r="I43" s="3">
-        <v>1820100</v>
+        <v>1794900</v>
       </c>
       <c r="J43" s="3">
-        <v>1823100</v>
+        <v>1797900</v>
       </c>
       <c r="K43" s="3">
         <v>1076000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>357700</v>
+        <v>352700</v>
       </c>
       <c r="E44" s="3">
-        <v>396800</v>
+        <v>391300</v>
       </c>
       <c r="F44" s="3">
-        <v>331100</v>
+        <v>326500</v>
       </c>
       <c r="G44" s="3">
-        <v>300800</v>
+        <v>296600</v>
       </c>
       <c r="H44" s="3">
-        <v>322900</v>
+        <v>318500</v>
       </c>
       <c r="I44" s="3">
-        <v>277900</v>
+        <v>274000</v>
       </c>
       <c r="J44" s="3">
-        <v>280800</v>
+        <v>276900</v>
       </c>
       <c r="K44" s="3">
         <v>231200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>530600</v>
+        <v>523200</v>
       </c>
       <c r="E45" s="3">
-        <v>517300</v>
+        <v>510100</v>
       </c>
       <c r="F45" s="3">
-        <v>399800</v>
+        <v>394300</v>
       </c>
       <c r="G45" s="3">
-        <v>354700</v>
+        <v>349800</v>
       </c>
       <c r="H45" s="3">
-        <v>410100</v>
+        <v>404500</v>
       </c>
       <c r="I45" s="3">
-        <v>434500</v>
+        <v>428500</v>
       </c>
       <c r="J45" s="3">
-        <v>377600</v>
+        <v>372400</v>
       </c>
       <c r="K45" s="3">
         <v>177400</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4665200</v>
+        <v>4600700</v>
       </c>
       <c r="E46" s="3">
-        <v>4501900</v>
+        <v>4439600</v>
       </c>
       <c r="F46" s="3">
-        <v>3718600</v>
+        <v>3667100</v>
       </c>
       <c r="G46" s="3">
-        <v>3456300</v>
+        <v>3408400</v>
       </c>
       <c r="H46" s="3">
-        <v>3216800</v>
+        <v>3172300</v>
       </c>
       <c r="I46" s="3">
-        <v>2838500</v>
+        <v>2799200</v>
       </c>
       <c r="J46" s="3">
-        <v>2857700</v>
+        <v>2818100</v>
       </c>
       <c r="K46" s="3">
         <v>1798600</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1374500</v>
+        <v>1355500</v>
       </c>
       <c r="E47" s="3">
-        <v>1192700</v>
+        <v>1176200</v>
       </c>
       <c r="F47" s="3">
-        <v>1118100</v>
+        <v>1102600</v>
       </c>
       <c r="G47" s="3">
-        <v>775200</v>
+        <v>764500</v>
       </c>
       <c r="H47" s="3">
-        <v>402700</v>
+        <v>397200</v>
       </c>
       <c r="I47" s="3">
-        <v>444900</v>
+        <v>438700</v>
       </c>
       <c r="J47" s="3">
-        <v>357700</v>
+        <v>352700</v>
       </c>
       <c r="K47" s="3">
         <v>60300</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12746100</v>
+        <v>12569700</v>
       </c>
       <c r="E48" s="3">
-        <v>12624900</v>
+        <v>12450100</v>
       </c>
       <c r="F48" s="3">
-        <v>11769200</v>
+        <v>11606200</v>
       </c>
       <c r="G48" s="3">
-        <v>11095200</v>
+        <v>10941600</v>
       </c>
       <c r="H48" s="3">
-        <v>10517300</v>
+        <v>10371700</v>
       </c>
       <c r="I48" s="3">
-        <v>8935100</v>
+        <v>8811400</v>
       </c>
       <c r="J48" s="3">
-        <v>8400800</v>
+        <v>8284500</v>
       </c>
       <c r="K48" s="3">
         <v>7607400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>22006400</v>
+        <v>21701700</v>
       </c>
       <c r="E49" s="3">
-        <v>20948100</v>
+        <v>20658200</v>
       </c>
       <c r="F49" s="3">
-        <v>18301800</v>
+        <v>18048500</v>
       </c>
       <c r="G49" s="3">
-        <v>16411500</v>
+        <v>16184300</v>
       </c>
       <c r="H49" s="3">
-        <v>13414900</v>
+        <v>13229200</v>
       </c>
       <c r="I49" s="3">
-        <v>11588100</v>
+        <v>11427700</v>
       </c>
       <c r="J49" s="3">
-        <v>11006500</v>
+        <v>10854200</v>
       </c>
       <c r="K49" s="3">
         <v>10287900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>691700</v>
+        <v>682100</v>
       </c>
       <c r="E52" s="3">
-        <v>671700</v>
+        <v>662400</v>
       </c>
       <c r="F52" s="3">
-        <v>559400</v>
+        <v>551700</v>
       </c>
       <c r="G52" s="3">
-        <v>240200</v>
+        <v>236800</v>
       </c>
       <c r="H52" s="3">
-        <v>518800</v>
+        <v>511600</v>
       </c>
       <c r="I52" s="3">
-        <v>622200</v>
+        <v>613600</v>
       </c>
       <c r="J52" s="3">
-        <v>325200</v>
+        <v>320700</v>
       </c>
       <c r="K52" s="3">
         <v>404900</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>41483900</v>
+        <v>40909700</v>
       </c>
       <c r="E54" s="3">
-        <v>39939500</v>
+        <v>39386600</v>
       </c>
       <c r="F54" s="3">
-        <v>35467100</v>
+        <v>34976100</v>
       </c>
       <c r="G54" s="3">
-        <v>31978300</v>
+        <v>31535600</v>
       </c>
       <c r="H54" s="3">
-        <v>28070500</v>
+        <v>27681900</v>
       </c>
       <c r="I54" s="3">
-        <v>24428800</v>
+        <v>24090600</v>
       </c>
       <c r="J54" s="3">
-        <v>22947900</v>
+        <v>22630200</v>
       </c>
       <c r="K54" s="3">
         <v>20159300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>736000</v>
+        <v>725800</v>
       </c>
       <c r="E57" s="3">
-        <v>1021300</v>
+        <v>1007100</v>
       </c>
       <c r="F57" s="3">
-        <v>896400</v>
+        <v>884000</v>
       </c>
       <c r="G57" s="3">
-        <v>638500</v>
+        <v>629600</v>
       </c>
       <c r="H57" s="3">
-        <v>659200</v>
+        <v>650100</v>
       </c>
       <c r="I57" s="3">
-        <v>506900</v>
+        <v>499900</v>
       </c>
       <c r="J57" s="3">
-        <v>529900</v>
+        <v>522500</v>
       </c>
       <c r="K57" s="3">
         <v>420200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3028400</v>
+        <v>2986500</v>
       </c>
       <c r="E58" s="3">
-        <v>1954600</v>
+        <v>1927600</v>
       </c>
       <c r="F58" s="3">
-        <v>2247300</v>
+        <v>2216200</v>
       </c>
       <c r="G58" s="3">
-        <v>1132100</v>
+        <v>1116500</v>
       </c>
       <c r="H58" s="3">
-        <v>1058200</v>
+        <v>1043600</v>
       </c>
       <c r="I58" s="3">
-        <v>691700</v>
+        <v>682100</v>
       </c>
       <c r="J58" s="3">
-        <v>1111400</v>
+        <v>1096100</v>
       </c>
       <c r="K58" s="3">
         <v>1037400</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3239700</v>
+        <v>3194900</v>
       </c>
       <c r="E59" s="3">
-        <v>3143700</v>
+        <v>3100100</v>
       </c>
       <c r="F59" s="3">
-        <v>2970000</v>
+        <v>2928900</v>
       </c>
       <c r="G59" s="3">
-        <v>2593100</v>
+        <v>2557200</v>
       </c>
       <c r="H59" s="3">
-        <v>2804500</v>
+        <v>2765600</v>
       </c>
       <c r="I59" s="3">
-        <v>2863600</v>
+        <v>2823900</v>
       </c>
       <c r="J59" s="3">
-        <v>2083200</v>
+        <v>2054400</v>
       </c>
       <c r="K59" s="3">
         <v>2141800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7004100</v>
+        <v>6907200</v>
       </c>
       <c r="E60" s="3">
-        <v>6119600</v>
+        <v>6034900</v>
       </c>
       <c r="F60" s="3">
-        <v>6113700</v>
+        <v>6029000</v>
       </c>
       <c r="G60" s="3">
-        <v>4363700</v>
+        <v>4303300</v>
       </c>
       <c r="H60" s="3">
-        <v>4119100</v>
+        <v>4062100</v>
       </c>
       <c r="I60" s="3">
-        <v>3579700</v>
+        <v>3530100</v>
       </c>
       <c r="J60" s="3">
-        <v>3724500</v>
+        <v>3673000</v>
       </c>
       <c r="K60" s="3">
         <v>3599400</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17259100</v>
+        <v>17020200</v>
       </c>
       <c r="E61" s="3">
-        <v>16624300</v>
+        <v>16394200</v>
       </c>
       <c r="F61" s="3">
-        <v>13246400</v>
+        <v>13063000</v>
       </c>
       <c r="G61" s="3">
-        <v>13934400</v>
+        <v>13741500</v>
       </c>
       <c r="H61" s="3">
-        <v>12667800</v>
+        <v>12492400</v>
       </c>
       <c r="I61" s="3">
-        <v>9802700</v>
+        <v>9667000</v>
       </c>
       <c r="J61" s="3">
-        <v>9057100</v>
+        <v>8931700</v>
       </c>
       <c r="K61" s="3">
         <v>8436200</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4434700</v>
+        <v>4373300</v>
       </c>
       <c r="E62" s="3">
-        <v>4146500</v>
+        <v>4089100</v>
       </c>
       <c r="F62" s="3">
-        <v>4239600</v>
+        <v>4180900</v>
       </c>
       <c r="G62" s="3">
-        <v>5075400</v>
+        <v>5005100</v>
       </c>
       <c r="H62" s="3">
-        <v>3463600</v>
+        <v>3415700</v>
       </c>
       <c r="I62" s="3">
-        <v>4005300</v>
+        <v>3949900</v>
       </c>
       <c r="J62" s="3">
-        <v>3176900</v>
+        <v>3132900</v>
       </c>
       <c r="K62" s="3">
         <v>2354100</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29577300</v>
+        <v>29167900</v>
       </c>
       <c r="E66" s="3">
-        <v>27695100</v>
+        <v>27311700</v>
       </c>
       <c r="F66" s="3">
-        <v>24296500</v>
+        <v>23960200</v>
       </c>
       <c r="G66" s="3">
-        <v>23080900</v>
+        <v>22761400</v>
       </c>
       <c r="H66" s="3">
-        <v>20275700</v>
+        <v>19995000</v>
       </c>
       <c r="I66" s="3">
-        <v>16847500</v>
+        <v>16614300</v>
       </c>
       <c r="J66" s="3">
-        <v>15989500</v>
+        <v>15768200</v>
       </c>
       <c r="K66" s="3">
         <v>14403500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2095000</v>
+        <v>2066000</v>
       </c>
       <c r="E72" s="3">
-        <v>3032800</v>
+        <v>2990800</v>
       </c>
       <c r="F72" s="3">
-        <v>3145100</v>
+        <v>3101600</v>
       </c>
       <c r="G72" s="3">
-        <v>2743100</v>
+        <v>2705200</v>
       </c>
       <c r="H72" s="3">
-        <v>3230100</v>
+        <v>3185400</v>
       </c>
       <c r="I72" s="3">
-        <v>3306200</v>
+        <v>3260500</v>
       </c>
       <c r="J72" s="3">
-        <v>2803700</v>
+        <v>2764900</v>
       </c>
       <c r="K72" s="3">
         <v>1798600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11906600</v>
+        <v>11741800</v>
       </c>
       <c r="E76" s="3">
-        <v>12244300</v>
+        <v>12074800</v>
       </c>
       <c r="F76" s="3">
-        <v>11170600</v>
+        <v>11015900</v>
       </c>
       <c r="G76" s="3">
-        <v>8897400</v>
+        <v>8774300</v>
       </c>
       <c r="H76" s="3">
-        <v>7794900</v>
+        <v>7687000</v>
       </c>
       <c r="I76" s="3">
-        <v>7581300</v>
+        <v>7476300</v>
       </c>
       <c r="J76" s="3">
-        <v>6958300</v>
+        <v>6862000</v>
       </c>
       <c r="K76" s="3">
         <v>5755700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>621500</v>
+        <v>612900</v>
       </c>
       <c r="E81" s="3">
-        <v>1193500</v>
+        <v>1176900</v>
       </c>
       <c r="F81" s="3">
-        <v>1223000</v>
+        <v>1206100</v>
       </c>
       <c r="G81" s="3">
-        <v>892000</v>
+        <v>879600</v>
       </c>
       <c r="H81" s="3">
-        <v>1290300</v>
+        <v>1272400</v>
       </c>
       <c r="I81" s="3">
-        <v>1182400</v>
+        <v>1166000</v>
       </c>
       <c r="J81" s="3">
-        <v>1152100</v>
+        <v>1136100</v>
       </c>
       <c r="K81" s="3">
         <v>889100</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3007000</v>
+        <v>2965300</v>
       </c>
       <c r="E83" s="3">
-        <v>2551000</v>
+        <v>2515700</v>
       </c>
       <c r="F83" s="3">
-        <v>2376600</v>
+        <v>2343700</v>
       </c>
       <c r="G83" s="3">
-        <v>2225800</v>
+        <v>2195000</v>
       </c>
       <c r="H83" s="3">
-        <v>1904400</v>
+        <v>1878000</v>
       </c>
       <c r="I83" s="3">
-        <v>1675300</v>
+        <v>1652100</v>
       </c>
       <c r="J83" s="3">
-        <v>1602900</v>
+        <v>1580700</v>
       </c>
       <c r="K83" s="3">
         <v>1488200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3324700</v>
+        <v>3278700</v>
       </c>
       <c r="E89" s="3">
-        <v>3555300</v>
+        <v>3506100</v>
       </c>
       <c r="F89" s="3">
-        <v>3242700</v>
+        <v>3197800</v>
       </c>
       <c r="G89" s="3">
-        <v>3380100</v>
+        <v>3333300</v>
       </c>
       <c r="H89" s="3">
-        <v>2902000</v>
+        <v>2861800</v>
       </c>
       <c r="I89" s="3">
-        <v>2998800</v>
+        <v>2957300</v>
       </c>
       <c r="J89" s="3">
-        <v>2916800</v>
+        <v>2876400</v>
       </c>
       <c r="K89" s="3">
         <v>2340200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1937600</v>
+        <v>-1910800</v>
       </c>
       <c r="E91" s="3">
-        <v>-2432000</v>
+        <v>-2398300</v>
       </c>
       <c r="F91" s="3">
-        <v>-2355900</v>
+        <v>-2323300</v>
       </c>
       <c r="G91" s="3">
-        <v>-1974600</v>
+        <v>-1947200</v>
       </c>
       <c r="H91" s="3">
-        <v>-2048500</v>
+        <v>-2020100</v>
       </c>
       <c r="I91" s="3">
-        <v>-1761000</v>
+        <v>-1736600</v>
       </c>
       <c r="J91" s="3">
-        <v>-1837100</v>
+        <v>-1811700</v>
       </c>
       <c r="K91" s="3">
         <v>-1714300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3508700</v>
+        <v>-3460200</v>
       </c>
       <c r="E94" s="3">
-        <v>-3996500</v>
+        <v>-3941100</v>
       </c>
       <c r="F94" s="3">
-        <v>-4039300</v>
+        <v>-3983400</v>
       </c>
       <c r="G94" s="3">
-        <v>-4555900</v>
+        <v>-4492800</v>
       </c>
       <c r="H94" s="3">
-        <v>-3727500</v>
+        <v>-3675900</v>
       </c>
       <c r="I94" s="3">
-        <v>-2200000</v>
+        <v>-2169500</v>
       </c>
       <c r="J94" s="3">
-        <v>-2692100</v>
+        <v>-2654900</v>
       </c>
       <c r="K94" s="3">
         <v>-2125100</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-971800</v>
+        <v>-958300</v>
       </c>
       <c r="E96" s="3">
-        <v>-877900</v>
+        <v>-865800</v>
       </c>
       <c r="F96" s="3">
-        <v>-772200</v>
+        <v>-761600</v>
       </c>
       <c r="G96" s="3">
-        <v>-687300</v>
+        <v>-677700</v>
       </c>
       <c r="H96" s="3">
-        <v>-849100</v>
+        <v>-837300</v>
       </c>
       <c r="I96" s="3">
-        <v>-843200</v>
+        <v>-831500</v>
       </c>
       <c r="J96" s="3">
-        <v>-799600</v>
+        <v>-788500</v>
       </c>
       <c r="K96" s="3">
         <v>-777900</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>102700</v>
+        <v>101300</v>
       </c>
       <c r="E100" s="3">
-        <v>626700</v>
+        <v>618000</v>
       </c>
       <c r="F100" s="3">
-        <v>704300</v>
+        <v>694500</v>
       </c>
       <c r="G100" s="3">
-        <v>1407000</v>
+        <v>1387600</v>
       </c>
       <c r="H100" s="3">
-        <v>914900</v>
+        <v>902200</v>
       </c>
       <c r="I100" s="3">
-        <v>-869100</v>
+        <v>-857000</v>
       </c>
       <c r="J100" s="3">
-        <v>-167800</v>
+        <v>-165400</v>
       </c>
       <c r="K100" s="3">
         <v>-63200</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-81300</v>
+        <v>-80200</v>
       </c>
       <c r="E102" s="3">
-        <v>185500</v>
+        <v>182900</v>
       </c>
       <c r="F102" s="3">
-        <v>-92400</v>
+        <v>-91100</v>
       </c>
       <c r="G102" s="3">
-        <v>231300</v>
+        <v>228100</v>
       </c>
       <c r="H102" s="3">
-        <v>89400</v>
+        <v>88200</v>
       </c>
       <c r="I102" s="3">
-        <v>-70200</v>
+        <v>-69200</v>
       </c>
       <c r="J102" s="3">
-        <v>56900</v>
+        <v>56100</v>
       </c>
       <c r="K102" s="3">
         <v>151900</v>

--- a/AAII_Financials/Yearly/TU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TU_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14578800</v>
+        <v>14725900</v>
       </c>
       <c r="E8" s="3">
-        <v>13330500</v>
+        <v>13464900</v>
       </c>
       <c r="F8" s="3">
-        <v>12270900</v>
+        <v>12394600</v>
       </c>
       <c r="G8" s="3">
-        <v>11179900</v>
+        <v>11292700</v>
       </c>
       <c r="H8" s="3">
-        <v>10631900</v>
+        <v>10739100</v>
       </c>
       <c r="I8" s="3">
-        <v>10271900</v>
+        <v>10375500</v>
       </c>
       <c r="J8" s="3">
-        <v>9696200</v>
+        <v>9793900</v>
       </c>
       <c r="K8" s="3">
         <v>9251200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5354200</v>
+        <v>5408200</v>
       </c>
       <c r="E9" s="3">
-        <v>5063400</v>
+        <v>5114500</v>
       </c>
       <c r="F9" s="3">
-        <v>4821500</v>
+        <v>4870100</v>
       </c>
       <c r="G9" s="3">
-        <v>4422100</v>
+        <v>4466700</v>
       </c>
       <c r="H9" s="3">
-        <v>4376200</v>
+        <v>4420300</v>
       </c>
       <c r="I9" s="3">
-        <v>4640700</v>
+        <v>4687500</v>
       </c>
       <c r="J9" s="3">
-        <v>4302600</v>
+        <v>4346000</v>
       </c>
       <c r="K9" s="3">
         <v>4093800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9224600</v>
+        <v>9317700</v>
       </c>
       <c r="E10" s="3">
-        <v>8267100</v>
+        <v>8350400</v>
       </c>
       <c r="F10" s="3">
-        <v>7449400</v>
+        <v>7524500</v>
       </c>
       <c r="G10" s="3">
-        <v>6757800</v>
+        <v>6825900</v>
       </c>
       <c r="H10" s="3">
-        <v>6255700</v>
+        <v>6318800</v>
       </c>
       <c r="I10" s="3">
-        <v>5631100</v>
+        <v>5687900</v>
       </c>
       <c r="J10" s="3">
-        <v>5393600</v>
+        <v>5448000</v>
       </c>
       <c r="K10" s="3">
         <v>5157400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>459100</v>
+        <v>463700</v>
       </c>
       <c r="E14" s="3">
-        <v>174900</v>
+        <v>176700</v>
       </c>
       <c r="F14" s="3">
-        <v>135500</v>
+        <v>136900</v>
       </c>
       <c r="G14" s="3">
-        <v>152300</v>
+        <v>153800</v>
       </c>
       <c r="H14" s="3">
-        <v>93300</v>
+        <v>94200</v>
       </c>
       <c r="I14" s="3">
-        <v>91800</v>
+        <v>92700</v>
       </c>
       <c r="J14" s="3">
-        <v>18900</v>
+        <v>19100</v>
       </c>
       <c r="K14" s="3">
         <v>81400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2965300</v>
+        <v>2995200</v>
       </c>
       <c r="E15" s="3">
-        <v>2515700</v>
+        <v>2541100</v>
       </c>
       <c r="F15" s="3">
-        <v>2343700</v>
+        <v>2367300</v>
       </c>
       <c r="G15" s="3">
-        <v>2195000</v>
+        <v>2217200</v>
       </c>
       <c r="H15" s="3">
-        <v>1878000</v>
+        <v>1897000</v>
       </c>
       <c r="I15" s="3">
-        <v>1652100</v>
+        <v>1668800</v>
       </c>
       <c r="J15" s="3">
-        <v>1580700</v>
+        <v>1596600</v>
       </c>
       <c r="K15" s="3">
         <v>1488200</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12857500</v>
+        <v>12987200</v>
       </c>
       <c r="E17" s="3">
-        <v>11177700</v>
+        <v>11290500</v>
       </c>
       <c r="F17" s="3">
-        <v>10030700</v>
+        <v>10131800</v>
       </c>
       <c r="G17" s="3">
-        <v>9371100</v>
+        <v>9465600</v>
       </c>
       <c r="H17" s="3">
-        <v>8462400</v>
+        <v>8547700</v>
       </c>
       <c r="I17" s="3">
-        <v>8204400</v>
+        <v>8287100</v>
       </c>
       <c r="J17" s="3">
-        <v>7698600</v>
+        <v>7776300</v>
       </c>
       <c r="K17" s="3">
         <v>7664900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1721300</v>
+        <v>1738700</v>
       </c>
       <c r="E18" s="3">
-        <v>2152800</v>
+        <v>2174500</v>
       </c>
       <c r="F18" s="3">
-        <v>2240200</v>
+        <v>2262800</v>
       </c>
       <c r="G18" s="3">
-        <v>1808800</v>
+        <v>1827000</v>
       </c>
       <c r="H18" s="3">
-        <v>2169500</v>
+        <v>2191400</v>
       </c>
       <c r="I18" s="3">
-        <v>2067500</v>
+        <v>2088300</v>
       </c>
       <c r="J18" s="3">
-        <v>1997500</v>
+        <v>2017700</v>
       </c>
       <c r="K18" s="3">
         <v>1586300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-12400</v>
+        <v>-12500</v>
       </c>
       <c r="E20" s="3">
-        <v>150900</v>
+        <v>152400</v>
       </c>
       <c r="F20" s="3">
-        <v>-25500</v>
+        <v>-25800</v>
       </c>
       <c r="G20" s="3">
-        <v>-41500</v>
+        <v>-42000</v>
       </c>
       <c r="H20" s="3">
-        <v>-34300</v>
+        <v>-34600</v>
       </c>
       <c r="I20" s="3">
-        <v>-41500</v>
+        <v>-42000</v>
       </c>
       <c r="J20" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="K20" s="3">
         <v>-21800</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4666700</v>
+        <v>4722500</v>
       </c>
       <c r="E21" s="3">
-        <v>4812900</v>
+        <v>4868800</v>
       </c>
       <c r="F21" s="3">
-        <v>4552400</v>
+        <v>4605200</v>
       </c>
       <c r="G21" s="3">
-        <v>3956700</v>
+        <v>4003000</v>
       </c>
       <c r="H21" s="3">
-        <v>4008500</v>
+        <v>4054500</v>
       </c>
       <c r="I21" s="3">
-        <v>3673800</v>
+        <v>3715800</v>
       </c>
       <c r="J21" s="3">
-        <v>3569100</v>
+        <v>3609700</v>
       </c>
       <c r="K21" s="3">
         <v>3061100</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>915300</v>
+        <v>924600</v>
       </c>
       <c r="E22" s="3">
-        <v>611400</v>
+        <v>617600</v>
       </c>
       <c r="F22" s="3">
-        <v>554600</v>
+        <v>560200</v>
       </c>
       <c r="G22" s="3">
-        <v>520300</v>
+        <v>525600</v>
       </c>
       <c r="H22" s="3">
-        <v>499900</v>
+        <v>505000</v>
       </c>
       <c r="I22" s="3">
-        <v>440200</v>
+        <v>444600</v>
       </c>
       <c r="J22" s="3">
-        <v>412500</v>
+        <v>416600</v>
       </c>
       <c r="K22" s="3">
         <v>356200</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>793600</v>
+        <v>801600</v>
       </c>
       <c r="E23" s="3">
-        <v>1692200</v>
+        <v>1709200</v>
       </c>
       <c r="F23" s="3">
-        <v>1660100</v>
+        <v>1676900</v>
       </c>
       <c r="G23" s="3">
-        <v>1246900</v>
+        <v>1259500</v>
       </c>
       <c r="H23" s="3">
-        <v>1635300</v>
+        <v>1651800</v>
       </c>
       <c r="I23" s="3">
-        <v>1585800</v>
+        <v>1601800</v>
       </c>
       <c r="J23" s="3">
-        <v>1580000</v>
+        <v>1595900</v>
       </c>
       <c r="K23" s="3">
         <v>1208300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>161800</v>
+        <v>163400</v>
       </c>
       <c r="E24" s="3">
-        <v>440200</v>
+        <v>444600</v>
       </c>
       <c r="F24" s="3">
-        <v>422700</v>
+        <v>426900</v>
       </c>
       <c r="G24" s="3">
-        <v>328700</v>
+        <v>332000</v>
       </c>
       <c r="H24" s="3">
-        <v>341100</v>
+        <v>344500</v>
       </c>
       <c r="I24" s="3">
-        <v>402300</v>
+        <v>406300</v>
       </c>
       <c r="J24" s="3">
-        <v>430000</v>
+        <v>434300</v>
       </c>
       <c r="K24" s="3">
         <v>309700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>631800</v>
+        <v>638200</v>
       </c>
       <c r="E26" s="3">
-        <v>1252000</v>
+        <v>1264600</v>
       </c>
       <c r="F26" s="3">
-        <v>1237400</v>
+        <v>1249900</v>
       </c>
       <c r="G26" s="3">
-        <v>918200</v>
+        <v>927500</v>
       </c>
       <c r="H26" s="3">
-        <v>1294300</v>
+        <v>1307300</v>
       </c>
       <c r="I26" s="3">
-        <v>1183500</v>
+        <v>1195400</v>
       </c>
       <c r="J26" s="3">
-        <v>1150000</v>
+        <v>1161600</v>
       </c>
       <c r="K26" s="3">
         <v>898600</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>612900</v>
+        <v>619100</v>
       </c>
       <c r="E27" s="3">
-        <v>1176900</v>
+        <v>1188800</v>
       </c>
       <c r="F27" s="3">
-        <v>1206100</v>
+        <v>1218300</v>
       </c>
       <c r="G27" s="3">
-        <v>879600</v>
+        <v>888500</v>
       </c>
       <c r="H27" s="3">
-        <v>1272400</v>
+        <v>1285200</v>
       </c>
       <c r="I27" s="3">
-        <v>1166000</v>
+        <v>1177800</v>
       </c>
       <c r="J27" s="3">
-        <v>1136100</v>
+        <v>1147600</v>
       </c>
       <c r="K27" s="3">
         <v>889100</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>12400</v>
+        <v>12500</v>
       </c>
       <c r="E32" s="3">
-        <v>-150900</v>
+        <v>-152400</v>
       </c>
       <c r="F32" s="3">
-        <v>25500</v>
+        <v>25800</v>
       </c>
       <c r="G32" s="3">
-        <v>41500</v>
+        <v>42000</v>
       </c>
       <c r="H32" s="3">
-        <v>34300</v>
+        <v>34600</v>
       </c>
       <c r="I32" s="3">
-        <v>41500</v>
+        <v>42000</v>
       </c>
       <c r="J32" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="K32" s="3">
         <v>21800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>612900</v>
+        <v>619100</v>
       </c>
       <c r="E33" s="3">
-        <v>1176900</v>
+        <v>1188800</v>
       </c>
       <c r="F33" s="3">
-        <v>1206100</v>
+        <v>1218300</v>
       </c>
       <c r="G33" s="3">
-        <v>879600</v>
+        <v>888500</v>
       </c>
       <c r="H33" s="3">
-        <v>1272400</v>
+        <v>1285200</v>
       </c>
       <c r="I33" s="3">
-        <v>1166000</v>
+        <v>1177800</v>
       </c>
       <c r="J33" s="3">
-        <v>1136100</v>
+        <v>1147600</v>
       </c>
       <c r="K33" s="3">
         <v>889100</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>612900</v>
+        <v>619100</v>
       </c>
       <c r="E35" s="3">
-        <v>1176900</v>
+        <v>1188800</v>
       </c>
       <c r="F35" s="3">
-        <v>1206100</v>
+        <v>1218300</v>
       </c>
       <c r="G35" s="3">
-        <v>879600</v>
+        <v>888500</v>
       </c>
       <c r="H35" s="3">
-        <v>1272400</v>
+        <v>1285200</v>
       </c>
       <c r="I35" s="3">
-        <v>1166000</v>
+        <v>1177800</v>
       </c>
       <c r="J35" s="3">
-        <v>1136100</v>
+        <v>1147600</v>
       </c>
       <c r="K35" s="3">
         <v>889100</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>629600</v>
+        <v>636000</v>
       </c>
       <c r="E41" s="3">
-        <v>709800</v>
+        <v>717000</v>
       </c>
       <c r="F41" s="3">
-        <v>526900</v>
+        <v>532200</v>
       </c>
       <c r="G41" s="3">
-        <v>618000</v>
+        <v>624200</v>
       </c>
       <c r="H41" s="3">
-        <v>389900</v>
+        <v>393800</v>
       </c>
       <c r="I41" s="3">
-        <v>301700</v>
+        <v>304700</v>
       </c>
       <c r="J41" s="3">
-        <v>370900</v>
+        <v>374700</v>
       </c>
       <c r="K41" s="3">
         <v>314100</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3095000</v>
+        <v>3126300</v>
       </c>
       <c r="E43" s="3">
-        <v>2828300</v>
+        <v>2856800</v>
       </c>
       <c r="F43" s="3">
-        <v>2419500</v>
+        <v>2443900</v>
       </c>
       <c r="G43" s="3">
-        <v>2144000</v>
+        <v>2165600</v>
       </c>
       <c r="H43" s="3">
-        <v>2059500</v>
+        <v>2080200</v>
       </c>
       <c r="I43" s="3">
-        <v>1794900</v>
+        <v>1813000</v>
       </c>
       <c r="J43" s="3">
-        <v>1797900</v>
+        <v>1816000</v>
       </c>
       <c r="K43" s="3">
         <v>1076000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>352700</v>
+        <v>356300</v>
       </c>
       <c r="E44" s="3">
-        <v>391300</v>
+        <v>395300</v>
       </c>
       <c r="F44" s="3">
-        <v>326500</v>
+        <v>329800</v>
       </c>
       <c r="G44" s="3">
-        <v>296600</v>
+        <v>299600</v>
       </c>
       <c r="H44" s="3">
-        <v>318500</v>
+        <v>321700</v>
       </c>
       <c r="I44" s="3">
-        <v>274000</v>
+        <v>276800</v>
       </c>
       <c r="J44" s="3">
-        <v>276900</v>
+        <v>279700</v>
       </c>
       <c r="K44" s="3">
         <v>231200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>523200</v>
+        <v>528500</v>
       </c>
       <c r="E45" s="3">
-        <v>510100</v>
+        <v>515300</v>
       </c>
       <c r="F45" s="3">
-        <v>394300</v>
+        <v>398200</v>
       </c>
       <c r="G45" s="3">
-        <v>349800</v>
+        <v>353300</v>
       </c>
       <c r="H45" s="3">
-        <v>404500</v>
+        <v>408500</v>
       </c>
       <c r="I45" s="3">
-        <v>428500</v>
+        <v>432800</v>
       </c>
       <c r="J45" s="3">
-        <v>372400</v>
+        <v>376200</v>
       </c>
       <c r="K45" s="3">
         <v>177400</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4600700</v>
+        <v>4647100</v>
       </c>
       <c r="E46" s="3">
-        <v>4439600</v>
+        <v>4484400</v>
       </c>
       <c r="F46" s="3">
-        <v>3667100</v>
+        <v>3704100</v>
       </c>
       <c r="G46" s="3">
-        <v>3408400</v>
+        <v>3442800</v>
       </c>
       <c r="H46" s="3">
-        <v>3172300</v>
+        <v>3204300</v>
       </c>
       <c r="I46" s="3">
-        <v>2799200</v>
+        <v>2827400</v>
       </c>
       <c r="J46" s="3">
-        <v>2818100</v>
+        <v>2846500</v>
       </c>
       <c r="K46" s="3">
         <v>1798600</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1355500</v>
+        <v>1369200</v>
       </c>
       <c r="E47" s="3">
-        <v>1176200</v>
+        <v>1188100</v>
       </c>
       <c r="F47" s="3">
-        <v>1102600</v>
+        <v>1113700</v>
       </c>
       <c r="G47" s="3">
-        <v>764500</v>
+        <v>772200</v>
       </c>
       <c r="H47" s="3">
-        <v>397200</v>
+        <v>401200</v>
       </c>
       <c r="I47" s="3">
-        <v>438700</v>
+        <v>443100</v>
       </c>
       <c r="J47" s="3">
-        <v>352700</v>
+        <v>356300</v>
       </c>
       <c r="K47" s="3">
         <v>60300</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12569700</v>
+        <v>12696400</v>
       </c>
       <c r="E48" s="3">
-        <v>12450100</v>
+        <v>12575700</v>
       </c>
       <c r="F48" s="3">
-        <v>11606200</v>
+        <v>11723300</v>
       </c>
       <c r="G48" s="3">
-        <v>10941600</v>
+        <v>11052000</v>
       </c>
       <c r="H48" s="3">
-        <v>10371700</v>
+        <v>10476300</v>
       </c>
       <c r="I48" s="3">
-        <v>8811400</v>
+        <v>8900300</v>
       </c>
       <c r="J48" s="3">
-        <v>8284500</v>
+        <v>8368100</v>
       </c>
       <c r="K48" s="3">
         <v>7607400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>21701700</v>
+        <v>21920600</v>
       </c>
       <c r="E49" s="3">
-        <v>20658200</v>
+        <v>20866500</v>
       </c>
       <c r="F49" s="3">
-        <v>18048500</v>
+        <v>18230500</v>
       </c>
       <c r="G49" s="3">
-        <v>16184300</v>
+        <v>16347500</v>
       </c>
       <c r="H49" s="3">
-        <v>13229200</v>
+        <v>13362600</v>
       </c>
       <c r="I49" s="3">
-        <v>11427700</v>
+        <v>11542900</v>
       </c>
       <c r="J49" s="3">
-        <v>10854200</v>
+        <v>10963600</v>
       </c>
       <c r="K49" s="3">
         <v>10287900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>682100</v>
+        <v>689000</v>
       </c>
       <c r="E52" s="3">
-        <v>662400</v>
+        <v>669100</v>
       </c>
       <c r="F52" s="3">
-        <v>551700</v>
+        <v>557200</v>
       </c>
       <c r="G52" s="3">
-        <v>236800</v>
+        <v>239200</v>
       </c>
       <c r="H52" s="3">
-        <v>511600</v>
+        <v>516700</v>
       </c>
       <c r="I52" s="3">
-        <v>613600</v>
+        <v>619800</v>
       </c>
       <c r="J52" s="3">
-        <v>320700</v>
+        <v>323900</v>
       </c>
       <c r="K52" s="3">
         <v>404900</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>40909700</v>
+        <v>41322300</v>
       </c>
       <c r="E54" s="3">
-        <v>39386600</v>
+        <v>39783800</v>
       </c>
       <c r="F54" s="3">
-        <v>34976100</v>
+        <v>35328900</v>
       </c>
       <c r="G54" s="3">
-        <v>31535600</v>
+        <v>31853700</v>
       </c>
       <c r="H54" s="3">
-        <v>27681900</v>
+        <v>27961100</v>
       </c>
       <c r="I54" s="3">
-        <v>24090600</v>
+        <v>24333600</v>
       </c>
       <c r="J54" s="3">
-        <v>22630200</v>
+        <v>22858400</v>
       </c>
       <c r="K54" s="3">
         <v>20159300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>725800</v>
+        <v>733200</v>
       </c>
       <c r="E57" s="3">
-        <v>1007100</v>
+        <v>1017300</v>
       </c>
       <c r="F57" s="3">
-        <v>884000</v>
+        <v>892900</v>
       </c>
       <c r="G57" s="3">
-        <v>629600</v>
+        <v>636000</v>
       </c>
       <c r="H57" s="3">
-        <v>650100</v>
+        <v>656600</v>
       </c>
       <c r="I57" s="3">
-        <v>499900</v>
+        <v>505000</v>
       </c>
       <c r="J57" s="3">
-        <v>522500</v>
+        <v>527800</v>
       </c>
       <c r="K57" s="3">
         <v>420200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2986500</v>
+        <v>3016600</v>
       </c>
       <c r="E58" s="3">
-        <v>1927600</v>
+        <v>1947000</v>
       </c>
       <c r="F58" s="3">
-        <v>2216200</v>
+        <v>2238500</v>
       </c>
       <c r="G58" s="3">
-        <v>1116500</v>
+        <v>1127700</v>
       </c>
       <c r="H58" s="3">
-        <v>1043600</v>
+        <v>1054100</v>
       </c>
       <c r="I58" s="3">
-        <v>682100</v>
+        <v>689000</v>
       </c>
       <c r="J58" s="3">
-        <v>1096100</v>
+        <v>1107100</v>
       </c>
       <c r="K58" s="3">
         <v>1037400</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3194900</v>
+        <v>3227100</v>
       </c>
       <c r="E59" s="3">
-        <v>3100100</v>
+        <v>3131400</v>
       </c>
       <c r="F59" s="3">
-        <v>2928900</v>
+        <v>2958400</v>
       </c>
       <c r="G59" s="3">
-        <v>2557200</v>
+        <v>2583000</v>
       </c>
       <c r="H59" s="3">
-        <v>2765600</v>
+        <v>2793500</v>
       </c>
       <c r="I59" s="3">
-        <v>2823900</v>
+        <v>2852400</v>
       </c>
       <c r="J59" s="3">
-        <v>2054400</v>
+        <v>2075100</v>
       </c>
       <c r="K59" s="3">
         <v>2141800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6907200</v>
+        <v>6976900</v>
       </c>
       <c r="E60" s="3">
-        <v>6034900</v>
+        <v>6095700</v>
       </c>
       <c r="F60" s="3">
-        <v>6029000</v>
+        <v>6089800</v>
       </c>
       <c r="G60" s="3">
-        <v>4303300</v>
+        <v>4346700</v>
       </c>
       <c r="H60" s="3">
-        <v>4062100</v>
+        <v>4103100</v>
       </c>
       <c r="I60" s="3">
-        <v>3530100</v>
+        <v>3565700</v>
       </c>
       <c r="J60" s="3">
-        <v>3673000</v>
+        <v>3710000</v>
       </c>
       <c r="K60" s="3">
         <v>3599400</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17020200</v>
+        <v>17191800</v>
       </c>
       <c r="E61" s="3">
-        <v>16394200</v>
+        <v>16559500</v>
       </c>
       <c r="F61" s="3">
-        <v>13063000</v>
+        <v>13194800</v>
       </c>
       <c r="G61" s="3">
-        <v>13741500</v>
+        <v>13880100</v>
       </c>
       <c r="H61" s="3">
-        <v>12492400</v>
+        <v>12618400</v>
       </c>
       <c r="I61" s="3">
-        <v>9667000</v>
+        <v>9764500</v>
       </c>
       <c r="J61" s="3">
-        <v>8931700</v>
+        <v>9021800</v>
       </c>
       <c r="K61" s="3">
         <v>8436200</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4373300</v>
+        <v>4417400</v>
       </c>
       <c r="E62" s="3">
-        <v>4089100</v>
+        <v>4130300</v>
       </c>
       <c r="F62" s="3">
-        <v>4180900</v>
+        <v>4223100</v>
       </c>
       <c r="G62" s="3">
-        <v>5005100</v>
+        <v>5055600</v>
       </c>
       <c r="H62" s="3">
-        <v>3415700</v>
+        <v>3450100</v>
       </c>
       <c r="I62" s="3">
-        <v>3949900</v>
+        <v>3989700</v>
       </c>
       <c r="J62" s="3">
-        <v>3132900</v>
+        <v>3164500</v>
       </c>
       <c r="K62" s="3">
         <v>2354100</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29167900</v>
+        <v>29462100</v>
       </c>
       <c r="E66" s="3">
-        <v>27311700</v>
+        <v>27587200</v>
       </c>
       <c r="F66" s="3">
-        <v>23960200</v>
+        <v>24201800</v>
       </c>
       <c r="G66" s="3">
-        <v>22761400</v>
+        <v>22990900</v>
       </c>
       <c r="H66" s="3">
-        <v>19995000</v>
+        <v>20196700</v>
       </c>
       <c r="I66" s="3">
-        <v>16614300</v>
+        <v>16781800</v>
       </c>
       <c r="J66" s="3">
-        <v>15768200</v>
+        <v>15927200</v>
       </c>
       <c r="K66" s="3">
         <v>14403500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2066000</v>
+        <v>2086900</v>
       </c>
       <c r="E72" s="3">
-        <v>2990800</v>
+        <v>3021000</v>
       </c>
       <c r="F72" s="3">
-        <v>3101600</v>
+        <v>3132900</v>
       </c>
       <c r="G72" s="3">
-        <v>2705200</v>
+        <v>2732400</v>
       </c>
       <c r="H72" s="3">
-        <v>3185400</v>
+        <v>3217500</v>
       </c>
       <c r="I72" s="3">
-        <v>3260500</v>
+        <v>3293400</v>
       </c>
       <c r="J72" s="3">
-        <v>2764900</v>
+        <v>2792800</v>
       </c>
       <c r="K72" s="3">
         <v>1798600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11741800</v>
+        <v>11860200</v>
       </c>
       <c r="E76" s="3">
-        <v>12074800</v>
+        <v>12196600</v>
       </c>
       <c r="F76" s="3">
-        <v>11015900</v>
+        <v>11127000</v>
       </c>
       <c r="G76" s="3">
-        <v>8774300</v>
+        <v>8862800</v>
       </c>
       <c r="H76" s="3">
-        <v>7687000</v>
+        <v>7764500</v>
       </c>
       <c r="I76" s="3">
-        <v>7476300</v>
+        <v>7551800</v>
       </c>
       <c r="J76" s="3">
-        <v>6862000</v>
+        <v>6931200</v>
       </c>
       <c r="K76" s="3">
         <v>5755700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>612900</v>
+        <v>619100</v>
       </c>
       <c r="E81" s="3">
-        <v>1176900</v>
+        <v>1188800</v>
       </c>
       <c r="F81" s="3">
-        <v>1206100</v>
+        <v>1218300</v>
       </c>
       <c r="G81" s="3">
-        <v>879600</v>
+        <v>888500</v>
       </c>
       <c r="H81" s="3">
-        <v>1272400</v>
+        <v>1285200</v>
       </c>
       <c r="I81" s="3">
-        <v>1166000</v>
+        <v>1177800</v>
       </c>
       <c r="J81" s="3">
-        <v>1136100</v>
+        <v>1147600</v>
       </c>
       <c r="K81" s="3">
         <v>889100</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2965300</v>
+        <v>2995200</v>
       </c>
       <c r="E83" s="3">
-        <v>2515700</v>
+        <v>2541100</v>
       </c>
       <c r="F83" s="3">
-        <v>2343700</v>
+        <v>2367300</v>
       </c>
       <c r="G83" s="3">
-        <v>2195000</v>
+        <v>2217200</v>
       </c>
       <c r="H83" s="3">
-        <v>1878000</v>
+        <v>1897000</v>
       </c>
       <c r="I83" s="3">
-        <v>1652100</v>
+        <v>1668800</v>
       </c>
       <c r="J83" s="3">
-        <v>1580700</v>
+        <v>1596600</v>
       </c>
       <c r="K83" s="3">
         <v>1488200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3278700</v>
+        <v>3311800</v>
       </c>
       <c r="E89" s="3">
-        <v>3506100</v>
+        <v>3541400</v>
       </c>
       <c r="F89" s="3">
-        <v>3197800</v>
+        <v>3230100</v>
       </c>
       <c r="G89" s="3">
-        <v>3333300</v>
+        <v>3367000</v>
       </c>
       <c r="H89" s="3">
-        <v>2861800</v>
+        <v>2890700</v>
       </c>
       <c r="I89" s="3">
-        <v>2957300</v>
+        <v>2987100</v>
       </c>
       <c r="J89" s="3">
-        <v>2876400</v>
+        <v>2905400</v>
       </c>
       <c r="K89" s="3">
         <v>2340200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1910800</v>
+        <v>-1930100</v>
       </c>
       <c r="E91" s="3">
-        <v>-2398300</v>
+        <v>-2422500</v>
       </c>
       <c r="F91" s="3">
-        <v>-2323300</v>
+        <v>-2346700</v>
       </c>
       <c r="G91" s="3">
-        <v>-1947200</v>
+        <v>-1966900</v>
       </c>
       <c r="H91" s="3">
-        <v>-2020100</v>
+        <v>-2040500</v>
       </c>
       <c r="I91" s="3">
-        <v>-1736600</v>
+        <v>-1754200</v>
       </c>
       <c r="J91" s="3">
-        <v>-1811700</v>
+        <v>-1830000</v>
       </c>
       <c r="K91" s="3">
         <v>-1714300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3460200</v>
+        <v>-3495100</v>
       </c>
       <c r="E94" s="3">
-        <v>-3941100</v>
+        <v>-3980900</v>
       </c>
       <c r="F94" s="3">
-        <v>-3983400</v>
+        <v>-4023600</v>
       </c>
       <c r="G94" s="3">
-        <v>-4492800</v>
+        <v>-4538100</v>
       </c>
       <c r="H94" s="3">
-        <v>-3675900</v>
+        <v>-3712900</v>
       </c>
       <c r="I94" s="3">
-        <v>-2169500</v>
+        <v>-2191400</v>
       </c>
       <c r="J94" s="3">
-        <v>-2654900</v>
+        <v>-2681600</v>
       </c>
       <c r="K94" s="3">
         <v>-2125100</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-958300</v>
+        <v>-968000</v>
       </c>
       <c r="E96" s="3">
-        <v>-865800</v>
+        <v>-874500</v>
       </c>
       <c r="F96" s="3">
-        <v>-761600</v>
+        <v>-769200</v>
       </c>
       <c r="G96" s="3">
-        <v>-677700</v>
+        <v>-684600</v>
       </c>
       <c r="H96" s="3">
-        <v>-837300</v>
+        <v>-845800</v>
       </c>
       <c r="I96" s="3">
-        <v>-831500</v>
+        <v>-839900</v>
       </c>
       <c r="J96" s="3">
-        <v>-788500</v>
+        <v>-796500</v>
       </c>
       <c r="K96" s="3">
         <v>-777900</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>101300</v>
+        <v>102300</v>
       </c>
       <c r="E100" s="3">
-        <v>618000</v>
+        <v>624200</v>
       </c>
       <c r="F100" s="3">
-        <v>694500</v>
+        <v>701500</v>
       </c>
       <c r="G100" s="3">
-        <v>1387600</v>
+        <v>1401600</v>
       </c>
       <c r="H100" s="3">
-        <v>902200</v>
+        <v>911300</v>
       </c>
       <c r="I100" s="3">
-        <v>-857000</v>
+        <v>-865700</v>
       </c>
       <c r="J100" s="3">
-        <v>-165400</v>
+        <v>-167100</v>
       </c>
       <c r="K100" s="3">
         <v>-63200</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-80200</v>
+        <v>-81000</v>
       </c>
       <c r="E102" s="3">
-        <v>182900</v>
+        <v>184800</v>
       </c>
       <c r="F102" s="3">
-        <v>-91100</v>
+        <v>-92000</v>
       </c>
       <c r="G102" s="3">
-        <v>228100</v>
+        <v>230400</v>
       </c>
       <c r="H102" s="3">
-        <v>88200</v>
+        <v>89100</v>
       </c>
       <c r="I102" s="3">
-        <v>-69200</v>
+        <v>-69900</v>
       </c>
       <c r="J102" s="3">
-        <v>56100</v>
+        <v>56700</v>
       </c>
       <c r="K102" s="3">
         <v>151900</v>

--- a/AAII_Financials/Yearly/TU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>TU</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14725900</v>
+        <v>15148100</v>
       </c>
       <c r="E8" s="3">
-        <v>13464900</v>
+        <v>13515400</v>
       </c>
       <c r="F8" s="3">
-        <v>12394600</v>
+        <v>13305500</v>
       </c>
       <c r="G8" s="3">
-        <v>11292700</v>
+        <v>12039700</v>
       </c>
       <c r="H8" s="3">
-        <v>10739100</v>
+        <v>11248000</v>
       </c>
       <c r="I8" s="3">
-        <v>10375500</v>
+        <v>10329500</v>
       </c>
       <c r="J8" s="3">
-        <v>9793900</v>
+        <v>10609400</v>
       </c>
       <c r="K8" s="3">
         <v>9251200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5408200</v>
+        <v>9824900</v>
       </c>
       <c r="E9" s="3">
-        <v>5114500</v>
+        <v>8699400</v>
       </c>
       <c r="F9" s="3">
-        <v>4870100</v>
+        <v>8540600</v>
       </c>
       <c r="G9" s="3">
-        <v>4466700</v>
+        <v>7633000</v>
       </c>
       <c r="H9" s="3">
-        <v>4420300</v>
+        <v>6916500</v>
       </c>
       <c r="I9" s="3">
-        <v>4687500</v>
+        <v>6569200</v>
       </c>
       <c r="J9" s="3">
-        <v>4346000</v>
+        <v>6687800</v>
       </c>
       <c r="K9" s="3">
         <v>4093800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9317700</v>
+        <v>5323200</v>
       </c>
       <c r="E10" s="3">
-        <v>8350400</v>
+        <v>4815900</v>
       </c>
       <c r="F10" s="3">
-        <v>7524500</v>
+        <v>4765000</v>
       </c>
       <c r="G10" s="3">
-        <v>6825900</v>
+        <v>4406700</v>
       </c>
       <c r="H10" s="3">
-        <v>6318800</v>
+        <v>4331400</v>
       </c>
       <c r="I10" s="3">
-        <v>5687900</v>
+        <v>3760200</v>
       </c>
       <c r="J10" s="3">
-        <v>5448000</v>
+        <v>3921600</v>
       </c>
       <c r="K10" s="3">
         <v>5157400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>463700</v>
+        <v>484600</v>
       </c>
       <c r="E14" s="3">
-        <v>176700</v>
+        <v>101200</v>
       </c>
       <c r="F14" s="3">
-        <v>136900</v>
+        <v>-173100</v>
       </c>
       <c r="G14" s="3">
-        <v>153800</v>
+        <v>123200</v>
       </c>
       <c r="H14" s="3">
-        <v>94200</v>
+        <v>100200</v>
       </c>
       <c r="I14" s="3">
-        <v>92700</v>
+        <v>76200</v>
       </c>
       <c r="J14" s="3">
-        <v>19100</v>
+        <v>36700</v>
       </c>
       <c r="K14" s="3">
         <v>81400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2995200</v>
+        <v>3053800</v>
       </c>
       <c r="E15" s="3">
-        <v>2541100</v>
+        <v>2543900</v>
       </c>
       <c r="F15" s="3">
-        <v>2367300</v>
+        <v>2535800</v>
       </c>
       <c r="G15" s="3">
-        <v>2217200</v>
+        <v>2345800</v>
       </c>
       <c r="H15" s="3">
-        <v>1897000</v>
+        <v>1983000</v>
       </c>
       <c r="I15" s="3">
-        <v>1668800</v>
+        <v>1661400</v>
       </c>
       <c r="J15" s="3">
-        <v>1596600</v>
+        <v>1729600</v>
       </c>
       <c r="K15" s="3">
         <v>1488200</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12987200</v>
+        <v>12865100</v>
       </c>
       <c r="E17" s="3">
-        <v>11290500</v>
+        <v>11235200</v>
       </c>
       <c r="F17" s="3">
-        <v>10131800</v>
+        <v>11073200</v>
       </c>
       <c r="G17" s="3">
-        <v>9465600</v>
+        <v>9975700</v>
       </c>
       <c r="H17" s="3">
-        <v>8547700</v>
+        <v>8881000</v>
       </c>
       <c r="I17" s="3">
-        <v>8287100</v>
+        <v>8213800</v>
       </c>
       <c r="J17" s="3">
-        <v>7776300</v>
+        <v>8391800</v>
       </c>
       <c r="K17" s="3">
         <v>7664900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1738700</v>
+        <v>2283000</v>
       </c>
       <c r="E18" s="3">
-        <v>2174500</v>
+        <v>2280100</v>
       </c>
       <c r="F18" s="3">
-        <v>2262800</v>
+        <v>2232300</v>
       </c>
       <c r="G18" s="3">
-        <v>1827000</v>
+        <v>2064000</v>
       </c>
       <c r="H18" s="3">
-        <v>2191400</v>
+        <v>2366900</v>
       </c>
       <c r="I18" s="3">
-        <v>2088300</v>
+        <v>2115700</v>
       </c>
       <c r="J18" s="3">
-        <v>2017700</v>
+        <v>2217600</v>
       </c>
       <c r="K18" s="3">
         <v>1586300</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-12500</v>
+        <v>22000</v>
       </c>
       <c r="E20" s="3">
-        <v>152400</v>
+        <v>-155900</v>
       </c>
       <c r="F20" s="3">
-        <v>-25800</v>
+        <v>5500</v>
       </c>
       <c r="G20" s="3">
-        <v>-42000</v>
+        <v>33700</v>
       </c>
       <c r="H20" s="3">
-        <v>-34600</v>
+        <v>-800</v>
       </c>
       <c r="I20" s="3">
-        <v>-42000</v>
+        <v>-4400</v>
       </c>
       <c r="J20" s="3">
-        <v>-5200</v>
+        <v>-4000</v>
       </c>
       <c r="K20" s="3">
         <v>-21800</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4722500</v>
+        <v>5314900</v>
       </c>
       <c r="E21" s="3">
-        <v>4868800</v>
+        <v>4980000</v>
       </c>
       <c r="F21" s="3">
-        <v>4605200</v>
+        <v>4762600</v>
       </c>
       <c r="G21" s="3">
-        <v>4003000</v>
+        <v>4376100</v>
       </c>
       <c r="H21" s="3">
-        <v>4054500</v>
+        <v>4350700</v>
       </c>
       <c r="I21" s="3">
-        <v>3715800</v>
+        <v>3781500</v>
       </c>
       <c r="J21" s="3">
-        <v>3609700</v>
+        <v>3951100</v>
       </c>
       <c r="K21" s="3">
         <v>3061100</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>924600</v>
+        <v>973800</v>
       </c>
       <c r="E22" s="3">
-        <v>617600</v>
+        <v>634700</v>
       </c>
       <c r="F22" s="3">
-        <v>560200</v>
+        <v>615600</v>
       </c>
       <c r="G22" s="3">
-        <v>525600</v>
+        <v>572900</v>
       </c>
       <c r="H22" s="3">
-        <v>505000</v>
+        <v>545900</v>
       </c>
       <c r="I22" s="3">
-        <v>444600</v>
+        <v>458000</v>
       </c>
       <c r="J22" s="3">
-        <v>416600</v>
+        <v>461700</v>
       </c>
       <c r="K22" s="3">
         <v>356200</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>801600</v>
+        <v>824600</v>
       </c>
       <c r="E23" s="3">
-        <v>1709200</v>
+        <v>1715700</v>
       </c>
       <c r="F23" s="3">
-        <v>1676900</v>
+        <v>1800100</v>
       </c>
       <c r="G23" s="3">
-        <v>1259500</v>
+        <v>1342800</v>
       </c>
       <c r="H23" s="3">
-        <v>1651800</v>
+        <v>1730100</v>
       </c>
       <c r="I23" s="3">
-        <v>1601800</v>
+        <v>1594700</v>
       </c>
       <c r="J23" s="3">
-        <v>1595900</v>
+        <v>1728800</v>
       </c>
       <c r="K23" s="3">
         <v>1208300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>163400</v>
+        <v>168100</v>
       </c>
       <c r="E24" s="3">
-        <v>444600</v>
+        <v>446300</v>
       </c>
       <c r="F24" s="3">
-        <v>426900</v>
+        <v>458300</v>
       </c>
       <c r="G24" s="3">
-        <v>332000</v>
+        <v>353900</v>
       </c>
       <c r="H24" s="3">
-        <v>344500</v>
+        <v>360800</v>
       </c>
       <c r="I24" s="3">
-        <v>406300</v>
+        <v>404500</v>
       </c>
       <c r="J24" s="3">
-        <v>434300</v>
+        <v>470500</v>
       </c>
       <c r="K24" s="3">
         <v>309700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>638200</v>
+        <v>656500</v>
       </c>
       <c r="E26" s="3">
-        <v>1264600</v>
+        <v>1269400</v>
       </c>
       <c r="F26" s="3">
-        <v>1249900</v>
+        <v>1341800</v>
       </c>
       <c r="G26" s="3">
-        <v>927500</v>
+        <v>988900</v>
       </c>
       <c r="H26" s="3">
-        <v>1307300</v>
+        <v>1369300</v>
       </c>
       <c r="I26" s="3">
-        <v>1195400</v>
+        <v>1190100</v>
       </c>
       <c r="J26" s="3">
-        <v>1161600</v>
+        <v>1258300</v>
       </c>
       <c r="K26" s="3">
         <v>898600</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>619100</v>
+        <v>636800</v>
       </c>
       <c r="E27" s="3">
-        <v>1188800</v>
+        <v>1193300</v>
       </c>
       <c r="F27" s="3">
-        <v>1218300</v>
+        <v>1307800</v>
       </c>
       <c r="G27" s="3">
-        <v>888500</v>
+        <v>947300</v>
       </c>
       <c r="H27" s="3">
-        <v>1285200</v>
+        <v>1346200</v>
       </c>
       <c r="I27" s="3">
-        <v>1177800</v>
+        <v>1172600</v>
       </c>
       <c r="J27" s="3">
-        <v>1147600</v>
+        <v>1243100</v>
       </c>
       <c r="K27" s="3">
         <v>889100</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>12500</v>
+        <v>-22000</v>
       </c>
       <c r="E32" s="3">
-        <v>-152400</v>
+        <v>155900</v>
       </c>
       <c r="F32" s="3">
-        <v>25800</v>
+        <v>-5500</v>
       </c>
       <c r="G32" s="3">
-        <v>42000</v>
+        <v>-33700</v>
       </c>
       <c r="H32" s="3">
-        <v>34600</v>
+        <v>800</v>
       </c>
       <c r="I32" s="3">
-        <v>42000</v>
+        <v>4400</v>
       </c>
       <c r="J32" s="3">
-        <v>5200</v>
+        <v>4000</v>
       </c>
       <c r="K32" s="3">
         <v>21800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>619100</v>
+        <v>636800</v>
       </c>
       <c r="E33" s="3">
-        <v>1188800</v>
+        <v>1193300</v>
       </c>
       <c r="F33" s="3">
-        <v>1218300</v>
+        <v>1307800</v>
       </c>
       <c r="G33" s="3">
-        <v>888500</v>
+        <v>947300</v>
       </c>
       <c r="H33" s="3">
-        <v>1285200</v>
+        <v>1346100</v>
       </c>
       <c r="I33" s="3">
-        <v>1177800</v>
+        <v>1172600</v>
       </c>
       <c r="J33" s="3">
-        <v>1147600</v>
+        <v>1243100</v>
       </c>
       <c r="K33" s="3">
         <v>889100</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>619100</v>
+        <v>636800</v>
       </c>
       <c r="E35" s="3">
-        <v>1188800</v>
+        <v>1193300</v>
       </c>
       <c r="F35" s="3">
-        <v>1218300</v>
+        <v>1307800</v>
       </c>
       <c r="G35" s="3">
-        <v>888500</v>
+        <v>947300</v>
       </c>
       <c r="H35" s="3">
-        <v>1285200</v>
+        <v>1346100</v>
       </c>
       <c r="I35" s="3">
-        <v>1177800</v>
+        <v>1172600</v>
       </c>
       <c r="J35" s="3">
-        <v>1147600</v>
+        <v>1243100</v>
       </c>
       <c r="K35" s="3">
         <v>889100</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>636000</v>
+        <v>654200</v>
       </c>
       <c r="E41" s="3">
-        <v>717000</v>
+        <v>719700</v>
       </c>
       <c r="F41" s="3">
-        <v>532200</v>
+        <v>571300</v>
       </c>
       <c r="G41" s="3">
-        <v>624200</v>
+        <v>665500</v>
       </c>
       <c r="H41" s="3">
-        <v>393800</v>
+        <v>412500</v>
       </c>
       <c r="I41" s="3">
-        <v>304700</v>
+        <v>303400</v>
       </c>
       <c r="J41" s="3">
-        <v>374700</v>
+        <v>405900</v>
       </c>
       <c r="K41" s="3">
         <v>314100</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>19900</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3126300</v>
+        <v>3215900</v>
       </c>
       <c r="E43" s="3">
-        <v>2856800</v>
+        <v>2867600</v>
       </c>
       <c r="F43" s="3">
-        <v>2443900</v>
+        <v>2629000</v>
       </c>
       <c r="G43" s="3">
-        <v>2165600</v>
+        <v>2308900</v>
       </c>
       <c r="H43" s="3">
-        <v>2080200</v>
+        <v>2178800</v>
       </c>
       <c r="I43" s="3">
-        <v>1813000</v>
+        <v>1805000</v>
       </c>
       <c r="J43" s="3">
-        <v>1816000</v>
+        <v>1967200</v>
       </c>
       <c r="K43" s="3">
         <v>1076000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>356300</v>
+        <v>366500</v>
       </c>
       <c r="E44" s="3">
-        <v>395300</v>
+        <v>396800</v>
       </c>
       <c r="F44" s="3">
-        <v>329800</v>
+        <v>354000</v>
       </c>
       <c r="G44" s="3">
-        <v>299600</v>
+        <v>319400</v>
       </c>
       <c r="H44" s="3">
-        <v>321700</v>
+        <v>336900</v>
       </c>
       <c r="I44" s="3">
-        <v>276800</v>
+        <v>275600</v>
       </c>
       <c r="J44" s="3">
-        <v>279700</v>
+        <v>303000</v>
       </c>
       <c r="K44" s="3">
         <v>231200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>528500</v>
+        <v>238500</v>
       </c>
       <c r="E45" s="3">
-        <v>515300</v>
+        <v>237200</v>
       </c>
       <c r="F45" s="3">
-        <v>398200</v>
+        <v>192800</v>
       </c>
       <c r="G45" s="3">
-        <v>353300</v>
+        <v>181300</v>
       </c>
       <c r="H45" s="3">
-        <v>408500</v>
+        <v>197400</v>
       </c>
       <c r="I45" s="3">
-        <v>432800</v>
+        <v>226400</v>
       </c>
       <c r="J45" s="3">
-        <v>376200</v>
+        <v>199300</v>
       </c>
       <c r="K45" s="3">
         <v>177400</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4647100</v>
+        <v>4780300</v>
       </c>
       <c r="E46" s="3">
-        <v>4484400</v>
+        <v>4501200</v>
       </c>
       <c r="F46" s="3">
-        <v>3704100</v>
+        <v>3976300</v>
       </c>
       <c r="G46" s="3">
-        <v>3442800</v>
+        <v>3670500</v>
       </c>
       <c r="H46" s="3">
-        <v>3204300</v>
+        <v>3356100</v>
       </c>
       <c r="I46" s="3">
-        <v>2827400</v>
+        <v>2814900</v>
       </c>
       <c r="J46" s="3">
-        <v>2846500</v>
+        <v>3083500</v>
       </c>
       <c r="K46" s="3">
         <v>1798600</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1369200</v>
+        <v>625500</v>
       </c>
       <c r="E47" s="3">
-        <v>1188100</v>
+        <v>450000</v>
       </c>
       <c r="F47" s="3">
-        <v>1113700</v>
+        <v>392700</v>
       </c>
       <c r="G47" s="3">
-        <v>772200</v>
+        <v>240200</v>
       </c>
       <c r="H47" s="3">
-        <v>401200</v>
+        <v>87100</v>
       </c>
       <c r="I47" s="3">
-        <v>443100</v>
+        <v>55000</v>
       </c>
       <c r="J47" s="3">
-        <v>356300</v>
+        <v>44700</v>
       </c>
       <c r="K47" s="3">
         <v>60300</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12696400</v>
+        <v>13060400</v>
       </c>
       <c r="E48" s="3">
-        <v>12575700</v>
+        <v>12622800</v>
       </c>
       <c r="F48" s="3">
-        <v>11723300</v>
+        <v>12584800</v>
       </c>
       <c r="G48" s="3">
-        <v>11052000</v>
+        <v>11783100</v>
       </c>
       <c r="H48" s="3">
-        <v>10476300</v>
+        <v>10972700</v>
       </c>
       <c r="I48" s="3">
-        <v>8900300</v>
+        <v>8860900</v>
       </c>
       <c r="J48" s="3">
-        <v>8368100</v>
+        <v>9064800</v>
       </c>
       <c r="K48" s="3">
         <v>7607400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>21920600</v>
+        <v>22549100</v>
       </c>
       <c r="E49" s="3">
-        <v>20866500</v>
+        <v>20961700</v>
       </c>
       <c r="F49" s="3">
-        <v>18230500</v>
+        <v>19561600</v>
       </c>
       <c r="G49" s="3">
-        <v>16347500</v>
+        <v>17429000</v>
       </c>
       <c r="H49" s="3">
-        <v>13362600</v>
+        <v>13995800</v>
       </c>
       <c r="I49" s="3">
-        <v>11542900</v>
+        <v>11491800</v>
       </c>
       <c r="J49" s="3">
-        <v>10963600</v>
+        <v>11876400</v>
       </c>
       <c r="K49" s="3">
         <v>10287900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>689000</v>
+        <v>514900</v>
       </c>
       <c r="E52" s="3">
-        <v>669100</v>
+        <v>543800</v>
       </c>
       <c r="F52" s="3">
-        <v>557200</v>
+        <v>530200</v>
       </c>
       <c r="G52" s="3">
-        <v>239200</v>
+        <v>165600</v>
       </c>
       <c r="H52" s="3">
-        <v>516700</v>
+        <v>283700</v>
       </c>
       <c r="I52" s="3">
-        <v>619800</v>
+        <v>502000</v>
       </c>
       <c r="J52" s="3">
-        <v>323900</v>
+        <v>253600</v>
       </c>
       <c r="K52" s="3">
         <v>404900</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>41322300</v>
+        <v>42507000</v>
       </c>
       <c r="E54" s="3">
-        <v>39783800</v>
+        <v>39949900</v>
       </c>
       <c r="F54" s="3">
-        <v>35328900</v>
+        <v>37916500</v>
       </c>
       <c r="G54" s="3">
-        <v>31853700</v>
+        <v>33960900</v>
       </c>
       <c r="H54" s="3">
-        <v>27961100</v>
+        <v>29286000</v>
       </c>
       <c r="I54" s="3">
-        <v>24333600</v>
+        <v>24225700</v>
       </c>
       <c r="J54" s="3">
-        <v>22858400</v>
+        <v>24761600</v>
       </c>
       <c r="K54" s="3">
         <v>20159300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>733200</v>
+        <v>754200</v>
       </c>
       <c r="E57" s="3">
-        <v>1017300</v>
+        <v>1021100</v>
       </c>
       <c r="F57" s="3">
-        <v>892900</v>
+        <v>958500</v>
       </c>
       <c r="G57" s="3">
-        <v>636000</v>
+        <v>671000</v>
       </c>
       <c r="H57" s="3">
-        <v>656600</v>
+        <v>687700</v>
       </c>
       <c r="I57" s="3">
-        <v>505000</v>
+        <v>502700</v>
       </c>
       <c r="J57" s="3">
-        <v>527800</v>
+        <v>571700</v>
       </c>
       <c r="K57" s="3">
         <v>420200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3016600</v>
+        <v>3116700</v>
       </c>
       <c r="E58" s="3">
-        <v>1947000</v>
+        <v>1964700</v>
       </c>
       <c r="F58" s="3">
-        <v>2238500</v>
+        <v>2418800</v>
       </c>
       <c r="G58" s="3">
-        <v>1127700</v>
+        <v>1211000</v>
       </c>
       <c r="H58" s="3">
-        <v>1054100</v>
+        <v>1117200</v>
       </c>
       <c r="I58" s="3">
-        <v>689000</v>
+        <v>692500</v>
       </c>
       <c r="J58" s="3">
-        <v>1107100</v>
+        <v>1214400</v>
       </c>
       <c r="K58" s="3">
         <v>1037400</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3227100</v>
+        <v>1329700</v>
       </c>
       <c r="E59" s="3">
-        <v>3131400</v>
+        <v>1237600</v>
       </c>
       <c r="F59" s="3">
-        <v>2958400</v>
+        <v>1190800</v>
       </c>
       <c r="G59" s="3">
-        <v>2583000</v>
+        <v>1091700</v>
       </c>
       <c r="H59" s="3">
-        <v>2793500</v>
+        <v>1060900</v>
       </c>
       <c r="I59" s="3">
-        <v>2852400</v>
+        <v>1023100</v>
       </c>
       <c r="J59" s="3">
-        <v>2075100</v>
+        <v>863600</v>
       </c>
       <c r="K59" s="3">
         <v>2141800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6976900</v>
+        <v>7176900</v>
       </c>
       <c r="E60" s="3">
-        <v>6095700</v>
+        <v>6122300</v>
       </c>
       <c r="F60" s="3">
-        <v>6089800</v>
+        <v>6537400</v>
       </c>
       <c r="G60" s="3">
-        <v>4346700</v>
+        <v>4634300</v>
       </c>
       <c r="H60" s="3">
-        <v>4103100</v>
+        <v>4297500</v>
       </c>
       <c r="I60" s="3">
-        <v>3565700</v>
+        <v>3549900</v>
       </c>
       <c r="J60" s="3">
-        <v>3710000</v>
+        <v>4018900</v>
       </c>
       <c r="K60" s="3">
         <v>3599400</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17191800</v>
+        <v>17829400</v>
       </c>
       <c r="E61" s="3">
-        <v>16559500</v>
+        <v>16639300</v>
       </c>
       <c r="F61" s="3">
-        <v>13194800</v>
+        <v>14222200</v>
       </c>
       <c r="G61" s="3">
-        <v>13880100</v>
+        <v>14919900</v>
       </c>
       <c r="H61" s="3">
-        <v>12618400</v>
+        <v>13236300</v>
       </c>
       <c r="I61" s="3">
-        <v>9764500</v>
+        <v>9723400</v>
       </c>
       <c r="J61" s="3">
-        <v>9021800</v>
+        <v>9833500</v>
       </c>
       <c r="K61" s="3">
         <v>8436200</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4417400</v>
+        <v>606500</v>
       </c>
       <c r="E62" s="3">
-        <v>4130300</v>
+        <v>443300</v>
       </c>
       <c r="F62" s="3">
-        <v>4223100</v>
+        <v>636900</v>
       </c>
       <c r="G62" s="3">
-        <v>5055600</v>
+        <v>788700</v>
       </c>
       <c r="H62" s="3">
-        <v>3450100</v>
+        <v>498800</v>
       </c>
       <c r="I62" s="3">
-        <v>3989700</v>
+        <v>633900</v>
       </c>
       <c r="J62" s="3">
-        <v>3164500</v>
+        <v>515100</v>
       </c>
       <c r="K62" s="3">
         <v>2354100</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>29462100</v>
+        <v>29405700</v>
       </c>
       <c r="E66" s="3">
-        <v>27587200</v>
+        <v>26903000</v>
       </c>
       <c r="F66" s="3">
-        <v>24201800</v>
+        <v>25226600</v>
       </c>
       <c r="G66" s="3">
-        <v>22990900</v>
+        <v>24097500</v>
       </c>
       <c r="H66" s="3">
-        <v>20196700</v>
+        <v>21068100</v>
       </c>
       <c r="I66" s="3">
-        <v>16781800</v>
+        <v>16647400</v>
       </c>
       <c r="J66" s="3">
-        <v>15927200</v>
+        <v>17219800</v>
       </c>
       <c r="K66" s="3">
         <v>14403500</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2086900</v>
+        <v>2146700</v>
       </c>
       <c r="E72" s="3">
-        <v>3021000</v>
+        <v>3032300</v>
       </c>
       <c r="F72" s="3">
-        <v>3132900</v>
+        <v>3363100</v>
       </c>
       <c r="G72" s="3">
-        <v>2732400</v>
+        <v>2913200</v>
       </c>
       <c r="H72" s="3">
-        <v>3217500</v>
+        <v>3370000</v>
       </c>
       <c r="I72" s="3">
-        <v>3293400</v>
+        <v>3278800</v>
       </c>
       <c r="J72" s="3">
-        <v>2792800</v>
+        <v>3025300</v>
       </c>
       <c r="K72" s="3">
         <v>1798600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11860200</v>
+        <v>12200200</v>
       </c>
       <c r="E76" s="3">
-        <v>12196600</v>
+        <v>12242300</v>
       </c>
       <c r="F76" s="3">
-        <v>11127000</v>
+        <v>11944800</v>
       </c>
       <c r="G76" s="3">
-        <v>8862800</v>
+        <v>9449100</v>
       </c>
       <c r="H76" s="3">
-        <v>7764500</v>
+        <v>8132400</v>
       </c>
       <c r="I76" s="3">
-        <v>7551800</v>
+        <v>7518300</v>
       </c>
       <c r="J76" s="3">
-        <v>6931200</v>
+        <v>7508300</v>
       </c>
       <c r="K76" s="3">
         <v>5755700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>619100</v>
+        <v>636800</v>
       </c>
       <c r="E81" s="3">
-        <v>1188800</v>
+        <v>1193300</v>
       </c>
       <c r="F81" s="3">
-        <v>1218300</v>
+        <v>1307800</v>
       </c>
       <c r="G81" s="3">
-        <v>888500</v>
+        <v>947300</v>
       </c>
       <c r="H81" s="3">
-        <v>1285200</v>
+        <v>1346100</v>
       </c>
       <c r="I81" s="3">
-        <v>1177800</v>
+        <v>1172600</v>
       </c>
       <c r="J81" s="3">
-        <v>1147600</v>
+        <v>1243100</v>
       </c>
       <c r="K81" s="3">
         <v>889100</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2995200</v>
+        <v>1848400</v>
       </c>
       <c r="E83" s="3">
-        <v>2541100</v>
+        <v>1638100</v>
       </c>
       <c r="F83" s="3">
-        <v>2367300</v>
+        <v>1674500</v>
       </c>
       <c r="G83" s="3">
-        <v>2217200</v>
+        <v>1635500</v>
       </c>
       <c r="H83" s="3">
-        <v>1897000</v>
+        <v>1483400</v>
       </c>
       <c r="I83" s="3">
-        <v>1668800</v>
+        <v>1223100</v>
       </c>
       <c r="J83" s="3">
-        <v>1596600</v>
+        <v>1289400</v>
       </c>
       <c r="K83" s="3">
         <v>1488200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3311800</v>
+        <v>3406700</v>
       </c>
       <c r="E89" s="3">
-        <v>3541400</v>
+        <v>3554700</v>
       </c>
       <c r="F89" s="3">
-        <v>3230100</v>
+        <v>3467400</v>
       </c>
       <c r="G89" s="3">
-        <v>3367000</v>
+        <v>3589700</v>
       </c>
       <c r="H89" s="3">
-        <v>2890700</v>
+        <v>3027700</v>
       </c>
       <c r="I89" s="3">
-        <v>2987100</v>
+        <v>2973900</v>
       </c>
       <c r="J89" s="3">
-        <v>2905400</v>
+        <v>3147300</v>
       </c>
       <c r="K89" s="3">
         <v>2340200</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1930100</v>
+        <v>-2409500</v>
       </c>
       <c r="E91" s="3">
-        <v>-2422500</v>
+        <v>-2694700</v>
       </c>
       <c r="F91" s="3">
-        <v>-2346700</v>
+        <v>-2447300</v>
       </c>
       <c r="G91" s="3">
-        <v>-1966900</v>
+        <v>-2214700</v>
       </c>
       <c r="H91" s="3">
-        <v>-2040500</v>
+        <v>-2276000</v>
       </c>
       <c r="I91" s="3">
-        <v>-1754200</v>
+        <v>-2106200</v>
       </c>
       <c r="J91" s="3">
-        <v>-1830000</v>
+        <v>-2456800</v>
       </c>
       <c r="K91" s="3">
         <v>-1714300</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3495100</v>
+        <v>-3595300</v>
       </c>
       <c r="E94" s="3">
-        <v>-3980900</v>
+        <v>-3995800</v>
       </c>
       <c r="F94" s="3">
-        <v>-4023600</v>
+        <v>-4319300</v>
       </c>
       <c r="G94" s="3">
-        <v>-4538100</v>
+        <v>-4838300</v>
       </c>
       <c r="H94" s="3">
-        <v>-3712900</v>
+        <v>-3888900</v>
       </c>
       <c r="I94" s="3">
-        <v>-2191400</v>
+        <v>-2181700</v>
       </c>
       <c r="J94" s="3">
-        <v>-2681600</v>
+        <v>-2904900</v>
       </c>
       <c r="K94" s="3">
         <v>-2125100</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-968000</v>
+        <v>995700</v>
       </c>
       <c r="E96" s="3">
-        <v>-874500</v>
+        <v>877800</v>
       </c>
       <c r="F96" s="3">
-        <v>-769200</v>
+        <v>825800</v>
       </c>
       <c r="G96" s="3">
-        <v>-684600</v>
+        <v>729900</v>
       </c>
       <c r="H96" s="3">
-        <v>-845800</v>
+        <v>885900</v>
       </c>
       <c r="I96" s="3">
-        <v>-839900</v>
+        <v>836200</v>
       </c>
       <c r="J96" s="3">
-        <v>-796500</v>
+        <v>862800</v>
       </c>
       <c r="K96" s="3">
         <v>-777900</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>102300</v>
+        <v>105300</v>
       </c>
       <c r="E100" s="3">
-        <v>624200</v>
+        <v>626600</v>
       </c>
       <c r="F100" s="3">
-        <v>701500</v>
+        <v>753100</v>
       </c>
       <c r="G100" s="3">
-        <v>1401600</v>
+        <v>1494300</v>
       </c>
       <c r="H100" s="3">
-        <v>911300</v>
+        <v>954500</v>
       </c>
       <c r="I100" s="3">
-        <v>-865700</v>
+        <v>-861800</v>
       </c>
       <c r="J100" s="3">
-        <v>-167100</v>
+        <v>-181000</v>
       </c>
       <c r="K100" s="3">
         <v>-63200</v>
@@ -4451,26 +4451,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-81000</v>
+        <v>-83300</v>
       </c>
       <c r="E102" s="3">
-        <v>184800</v>
+        <v>185500</v>
       </c>
       <c r="F102" s="3">
-        <v>-92000</v>
+        <v>-98800</v>
       </c>
       <c r="G102" s="3">
-        <v>230400</v>
+        <v>245600</v>
       </c>
       <c r="H102" s="3">
-        <v>89100</v>
+        <v>93300</v>
       </c>
       <c r="I102" s="3">
-        <v>-69900</v>
+        <v>-69600</v>
       </c>
       <c r="J102" s="3">
-        <v>56700</v>
+        <v>61400</v>
       </c>
       <c r="K102" s="3">
         <v>151900</v>

--- a/AAII_Financials/Yearly/TU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>TU</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>13996700</v>
+      </c>
+      <c r="E8" s="3">
         <v>15148100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13515400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13305500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12039700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11248000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10329500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10609400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9251200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9333200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9363300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8726700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8169300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7932000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9824900</v>
+        <v>9078100</v>
       </c>
       <c r="E9" s="3">
+        <v>9824100</v>
+      </c>
+      <c r="F9" s="3">
         <v>8699400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8540600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7633000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6916500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6569200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6687800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4093800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4153800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4160000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3819800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3628400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3630700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5323200</v>
+        <v>4918500</v>
       </c>
       <c r="E10" s="3">
+        <v>5324000</v>
+      </c>
+      <c r="F10" s="3">
         <v>4815900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4765000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4406700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4331400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3760200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3921600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5157400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5179400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5203300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4906800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4540800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4301300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>484600</v>
+        <v>239100</v>
       </c>
       <c r="E14" s="3">
+        <v>505100</v>
+      </c>
+      <c r="F14" s="3">
         <v>101200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-173100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>123200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>76200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>36700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>81400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>117100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>42400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>54700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>28600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2750100</v>
+      </c>
+      <c r="E15" s="3">
         <v>3053800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2543900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2535800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2345800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1983000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1661400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1729600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1488200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1433400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1439800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1388000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1404000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1390500</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12865100</v>
+        <v>11819200</v>
       </c>
       <c r="E17" s="3">
+        <v>12864300</v>
+      </c>
+      <c r="F17" s="3">
         <v>11235200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11073200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9975700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8881000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8213800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8391800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7664900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7566400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7374800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7336400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6956500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6420100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2283000</v>
+        <v>2177400</v>
       </c>
       <c r="E18" s="3">
+        <v>2283800</v>
+      </c>
+      <c r="F18" s="3">
         <v>2280100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2232300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2064000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2366900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2115700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2217600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1586300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1766800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1988500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1390300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1212700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1511900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>22000</v>
+        <v>-681800</v>
       </c>
       <c r="E20" s="3">
+        <v>-842000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-155900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>33700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-132700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>257100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>270300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5314900</v>
+        <v>5609400</v>
       </c>
       <c r="E21" s="3">
+        <v>6179600</v>
+      </c>
+      <c r="F21" s="3">
         <v>4980000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4762600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4376100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4350700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3781500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3951100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3061100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3186400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3290200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3032900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2887600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2915200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>973800</v>
+        <v>1793800</v>
       </c>
       <c r="E22" s="3">
+        <v>1818100</v>
+      </c>
+      <c r="F22" s="3">
         <v>634700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>615600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>572900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>545900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>458000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>461700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>356200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>343900</v>
       </c>
       <c r="M22" s="3">
         <v>343900</v>
       </c>
       <c r="N22" s="3">
+        <v>343900</v>
+      </c>
+      <c r="O22" s="3">
         <v>286400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>263500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>295800</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>853500</v>
+      </c>
+      <c r="E23" s="3">
         <v>824600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1715700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1800100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1342800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1730100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1594700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1728800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1208300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1431100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1512000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1361000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1219500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1222300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>201600</v>
+      </c>
+      <c r="E24" s="3">
         <v>168100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>446300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>458300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>353900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>360800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>404500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>470500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>309700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>393500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>393300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>364900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>313200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>288900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>651900</v>
+      </c>
+      <c r="E26" s="3">
         <v>656500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1269400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1341800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>988900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1369300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1190100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1258300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>898600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1037700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1118700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>996100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>906400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>933400</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>690100</v>
+      </c>
+      <c r="E27" s="3">
         <v>636800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1193300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1307800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>947300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1346200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1172600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1243100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>889100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1037700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1118700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>996100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>906400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>936500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-22000</v>
+        <v>681800</v>
       </c>
       <c r="E32" s="3">
+        <v>842000</v>
+      </c>
+      <c r="F32" s="3">
         <v>155900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-33700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>132700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-257100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-270300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>690100</v>
+      </c>
+      <c r="E33" s="3">
         <v>636800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1193300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1307800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>947300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1346100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1172600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1243100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>889100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1037700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1118700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>996100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>906400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>936500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>690100</v>
+      </c>
+      <c r="E35" s="3">
         <v>636800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1193300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1307800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>947300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1346100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1172600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1243100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>889100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1037700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1118700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>996100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>906400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>936500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,80 +2072,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>604000</v>
+      </c>
+      <c r="E41" s="3">
         <v>654200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>719700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>571300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>665500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>412500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>303400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>405900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>314100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>167400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>47100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>258700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>80500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>700</v>
+      </c>
+      <c r="E42" s="3">
         <v>13600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19900</v>
-      </c>
-      <c r="F42" s="3">
-        <v>1600</v>
       </c>
       <c r="G42" s="3">
         <v>1600</v>
       </c>
       <c r="H42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I42" s="3">
         <v>800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2076,324 +2165,348 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2998900</v>
+      </c>
+      <c r="E43" s="3">
         <v>3215900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2867600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2629000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2308900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2178800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1805000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1967200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1076000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1073000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1240400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1149300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1178900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1147700</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>437200</v>
+      </c>
+      <c r="E44" s="3">
         <v>366500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>396800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>354000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>319400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>336900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>275600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>303000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>231200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>270300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>251200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>251000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>263500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>271200</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E45" s="3">
         <v>238500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>237200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>192800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>181300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>197400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>226400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>199300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>177400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>239500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>177400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>133900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>140800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>121400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4619700</v>
+      </c>
+      <c r="E46" s="3">
         <v>4780300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4501200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3976300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3670500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3356100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2814900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3083500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1798600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1750300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1716100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1792900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1663700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1575600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>735300</v>
+      </c>
+      <c r="E47" s="3">
         <v>625500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>450000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>392700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>240200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>87100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>55000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>60300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>70600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>55000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>45400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>43700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12017300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13060400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12622800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12584800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11783100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10972700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8860900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9064800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7607400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7310400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7162000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6486500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6146500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6118200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21640300</v>
+      </c>
+      <c r="E49" s="3">
         <v>22549100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20961700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19561600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17429000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13995800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11491800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11876400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10287900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10321300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9070500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7904500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7439800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7539400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>428100</v>
+      </c>
+      <c r="E52" s="3">
         <v>514900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>543800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>530200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>165600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>283700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>502000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>253600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>404900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>374700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>223000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>371100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>97100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62200</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>40326200</v>
+      </c>
+      <c r="E54" s="3">
         <v>42507000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39949900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37916500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33960900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29286000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>24225700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24761600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20159300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19827200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18226500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16600400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15390800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15311600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>782600</v>
+      </c>
+      <c r="E57" s="3">
         <v>754200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1021100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>958500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>671000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>687700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>502700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>571700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>420200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>357400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>359600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>352600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>353100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>348000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2898200</v>
+      </c>
+      <c r="E58" s="3">
         <v>3116700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1964700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2418800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1211000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1117200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>692500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1214400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1037400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>717800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>278700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>307900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>712900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1129300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1329700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1237600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1190800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1091700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1060900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1023100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>863600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2141800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2135400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2108600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1879100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1583900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1476500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6832600</v>
+      </c>
+      <c r="E60" s="3">
         <v>7176900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6122300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6537400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4634300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4297500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3549900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4018900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3599400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3210700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2746900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2539600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2649800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2953800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17879700</v>
+      </c>
+      <c r="E61" s="3">
         <v>17829400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16639300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14222200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14919900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13236300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9723400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9833500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8436200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8396100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7108600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5768300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4299200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4231400</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>547000</v>
+      </c>
+      <c r="E62" s="3">
         <v>606500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>443300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>636900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>788700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>498800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>633900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>515100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2354100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2459800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2519200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2123900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2655800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2354600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28651600</v>
+      </c>
+      <c r="E66" s="3">
         <v>29405700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26903000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25226600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24097500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21068100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16647400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17219800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14403500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14066600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12374700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10431800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9604800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9539900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1056400</v>
+      </c>
+      <c r="E72" s="3">
         <v>2146700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3032300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3363100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2913200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3370000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3278800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3025300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1798600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1823100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1648600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1954600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1433300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1367400</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10856000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12200200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12242300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11944800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9449100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8132400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7518300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7508300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5755700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5760600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5851800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6170100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5785900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5771700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>690100</v>
+      </c>
+      <c r="E81" s="3">
         <v>636800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1193300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1307800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>947300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1346100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1172600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1243100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>889100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1037700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1118700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>996100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>906400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>936500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1689600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1848400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1638100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1674500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1635500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1483400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1223100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1289400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1488200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1433400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1439800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1388000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1404000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1390500</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3368700</v>
+      </c>
+      <c r="E89" s="3">
         <v>3406700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3554700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3467400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3589700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3027700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2973900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3147300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2340200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2670100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2674700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2498800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2423200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1959000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1911300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2409500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2694700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2447300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2214700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2276000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2106200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2456800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1714300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1536300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1505700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1266400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2644600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1418900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2571500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3595300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3995800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4319300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4838300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3888900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2181700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2904900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2125100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3361600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2879600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1839100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1549200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1511900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1085600</v>
+      </c>
+      <c r="E96" s="3">
         <v>995700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>877800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>825800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>729900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>885900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>836200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>862800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-777900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-744900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-716800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-655900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-582700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-493200</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,54 +4642,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-793700</v>
+      </c>
+      <c r="E100" s="3">
         <v>105300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>626600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>753100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1494300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>954500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-861800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-181000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-63200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>813900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-483400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-828100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-424800</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4472,8 +4720,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4490,52 +4738,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-83300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>185500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-98800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>245600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>93300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-69600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>61400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>151900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>122400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-216700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>176300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>45900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>22300</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>TU</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14839000</v>
+      </c>
+      <c r="E8" s="3">
         <v>13996700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15148100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>13515400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13305500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12039700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11248000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10329500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10609400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9251200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9333200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9363300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8726700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8169300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7932000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9600900</v>
+      </c>
+      <c r="E9" s="3">
         <v>9078100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9824100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8699400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8540600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7633000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6916500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6569200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6687800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4093800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4153800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4160000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3819800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3628400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3630700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5238100</v>
+      </c>
+      <c r="E10" s="3">
         <v>4918500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5324000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4815900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4765000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4406700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4331400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3760200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3921600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5157400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5179400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5203300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4906800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4540800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4301300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>436900</v>
+      </c>
+      <c r="E14" s="3">
         <v>239100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>505100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>101200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-173100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>123200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>76200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>36700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>81400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>117100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>42400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>54700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>28600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2947200</v>
+      </c>
+      <c r="E15" s="3">
         <v>2750100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3053800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2543900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2535800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2345800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1983000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1661400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1729600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1488200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1433400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1439800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1388000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1404000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1390500</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12503600</v>
+      </c>
+      <c r="E17" s="3">
         <v>11819200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12864300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11235200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11073200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9975700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8881000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8213800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8391800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7664900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7566400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7374800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7336400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6956500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6420100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2335300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2177400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2283800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2280100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2232300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2064000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2366900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2115700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2217600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1586300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1766800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1988500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1390300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1212700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1511900</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-681800</v>
+        <v>-39400</v>
       </c>
       <c r="E20" s="3">
+        <v>135500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-842000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-155900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>33700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-21800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-132700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>257100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>270300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6100</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5609400</v>
+        <v>5321900</v>
       </c>
       <c r="E21" s="3">
+        <v>4792100</v>
+      </c>
+      <c r="F21" s="3">
         <v>6179600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4980000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4762600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4376100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4350700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3781500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3951100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3061100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3186400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3290200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3032900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2887600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2915200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1793800</v>
+        <v>1102000</v>
       </c>
       <c r="E22" s="3">
+        <v>976500</v>
+      </c>
+      <c r="F22" s="3">
         <v>1818100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>634700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>615600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>572900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>545900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>458000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>461700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>356200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>343900</v>
       </c>
       <c r="N22" s="3">
         <v>343900</v>
       </c>
       <c r="O22" s="3">
+        <v>343900</v>
+      </c>
+      <c r="P22" s="3">
         <v>286400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>263500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>295800</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>876700</v>
+      </c>
+      <c r="E23" s="3">
         <v>853500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>824600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1715700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1342800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1730100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1594700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1728800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1208300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1431100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1512000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1361000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1219500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1222300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>310000</v>
+      </c>
+      <c r="E24" s="3">
         <v>201600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>168100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>446300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>458300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>353900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>360800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>404500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>470500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>309700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>393500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>393300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>364900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>313200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>288900</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>566700</v>
+      </c>
+      <c r="E26" s="3">
         <v>651900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>656500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1269400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1341800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>988900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1369300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1190100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1258300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>898600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1037700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1118700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>996100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>906400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>933400</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>811800</v>
+      </c>
+      <c r="E27" s="3">
         <v>690100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>636800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1193300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1307800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>947300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1346200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1172600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1243100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>889100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1037700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1118700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>996100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>906400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>936500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>681800</v>
+        <v>39400</v>
       </c>
       <c r="E32" s="3">
+        <v>-135500</v>
+      </c>
+      <c r="F32" s="3">
         <v>842000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>155900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-33700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>21800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>132700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-257100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-270300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6100</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>811700</v>
+      </c>
+      <c r="E33" s="3">
         <v>690100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>636800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1193300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1307800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>947300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1346100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1172600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1243100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>889100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1037700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1118700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>996100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>906400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>936500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>811700</v>
+      </c>
+      <c r="E35" s="3">
         <v>690100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>636800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1193300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1307800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>947300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1346100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1172600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1243100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>889100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1037700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1118700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>996100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>906400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>936500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,86 +2158,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1911600</v>
+      </c>
+      <c r="E41" s="3">
         <v>604000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>654200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>719700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>571300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>665500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>412500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>303400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>405900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>314100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>167400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>258700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>80500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19900</v>
-      </c>
-      <c r="G42" s="3">
-        <v>1600</v>
       </c>
       <c r="H42" s="3">
         <v>1600</v>
       </c>
       <c r="I42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J42" s="3">
         <v>800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2168,345 +2257,369 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2998900</v>
+        <v>3228700</v>
       </c>
       <c r="E43" s="3">
+        <v>2988500</v>
+      </c>
+      <c r="F43" s="3">
         <v>3215900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2867600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2629000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2308900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2178800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1805000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1967200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1076000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1073000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1240400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1149300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1178900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1147700</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>351500</v>
+      </c>
+      <c r="E44" s="3">
         <v>437200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>366500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>396800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>354000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>319400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>336900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>275600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>303000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>231200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>270300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>251200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>251000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>263500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>271200</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>230000</v>
+        <v>307000</v>
       </c>
       <c r="E45" s="3">
+        <v>298900</v>
+      </c>
+      <c r="F45" s="3">
         <v>238500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>237200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>192800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>181300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>197400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>226400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>199300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>177400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>239500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>177400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>133900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>140800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>121400</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4619700</v>
+        <v>6106000</v>
       </c>
       <c r="E46" s="3">
+        <v>4609300</v>
+      </c>
+      <c r="F46" s="3">
         <v>4780300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4501200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3976300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3670500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3356100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2814900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3083500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1798600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1750300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1716100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1792900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1663700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1575600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>848900</v>
+      </c>
+      <c r="E47" s="3">
         <v>735300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>625500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>450000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>392700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>240200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>87100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>55000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>60300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>70600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>55000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>45400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>43700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12731900</v>
+      </c>
+      <c r="E48" s="3">
         <v>12017300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13060400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12622800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12584800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11783100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10972700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8860900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9064800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7607400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7310400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7162000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6486500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6146500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6118200</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>21640300</v>
+        <v>22454600</v>
       </c>
       <c r="E49" s="3">
+        <v>21654200</v>
+      </c>
+      <c r="F49" s="3">
         <v>22549100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20961700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19561600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17429000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13995800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11491800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11876400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10287900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10321300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9070500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7904500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7439800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7539400</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>385100</v>
+      </c>
+      <c r="E52" s="3">
         <v>428100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>514900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>543800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>530200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>165600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>283700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>502000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>253600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>404900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>374700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>223000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>371100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>97100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>62200</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>40326200</v>
+        <v>43477600</v>
       </c>
       <c r="E54" s="3">
+        <v>40329700</v>
+      </c>
+      <c r="F54" s="3">
         <v>42507000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>39949900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37916500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33960900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29286000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24225700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24761600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20159300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19827200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18226500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16600400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15390800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15311600</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>716200</v>
+      </c>
+      <c r="E57" s="3">
         <v>782600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>754200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1021100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>958500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>671000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>687700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>502700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>571700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>420200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>357400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>359600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>352600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>353100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>348000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2940700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2898200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3116700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1964700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2418800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1211000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1117200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>692500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1214400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1037400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>717800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>278700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>307900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>712900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1129300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1324000</v>
+        <v>1501000</v>
       </c>
       <c r="E59" s="3">
+        <v>1415000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1329700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1237600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1190800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1091700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1060900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1023100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>863600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2141800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2135400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2108600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1879100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1583900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1476500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6832600</v>
+        <v>7066500</v>
       </c>
       <c r="E60" s="3">
+        <v>6836100</v>
+      </c>
+      <c r="F60" s="3">
         <v>7176900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6122300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6537400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4634300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4297500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3549900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4018900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3599400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3210700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2746900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2539600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2649800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2953800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17879700</v>
+        <v>20117100</v>
       </c>
       <c r="E61" s="3">
+        <v>17857400</v>
+      </c>
+      <c r="F61" s="3">
         <v>17829400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16639300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14222200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14919900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13236300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9723400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9833500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8436200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8396100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7108600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5768300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4299200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4231400</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>547000</v>
+        <v>522200</v>
       </c>
       <c r="E62" s="3">
+        <v>535200</v>
+      </c>
+      <c r="F62" s="3">
         <v>606500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>443300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>636900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>788700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>498800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>633900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>515100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2354100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2459800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2519200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2123900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2655800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2354600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>28651600</v>
+        <v>31386000</v>
       </c>
       <c r="E66" s="3">
+        <v>28655000</v>
+      </c>
+      <c r="F66" s="3">
         <v>29405700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26903000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25226600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24097500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21068100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16647400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17219800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14403500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14066600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12374700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10431800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9604800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9539900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1056400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2146700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3032300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3363100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2913200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3370000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3278800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3025300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1798600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1823100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1648600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1954600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1433300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1367400</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11505200</v>
+      </c>
+      <c r="E76" s="3">
         <v>10856000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12200200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12242300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11944800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9449100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8132400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7518300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7508300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5755700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5760600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5851800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6170100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5785900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5771700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>811700</v>
+      </c>
+      <c r="E81" s="3">
         <v>690100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>636800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1193300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1307800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>947300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1346100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1172600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1243100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>889100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1037700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1118700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>996100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>906400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>936500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1776600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1689600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1848400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1638100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1674500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1635500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1483400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1223100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1289400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1488200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1433400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1439800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1388000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1404000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1390500</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3548900</v>
+      </c>
+      <c r="E89" s="3">
         <v>3368700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3406700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3554700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3467400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3589700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3027700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2973900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3147300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2340200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2670100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2674700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2498800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2423200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1959000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1834300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1911300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2409500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2694700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2447300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2214700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2276000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2106200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2456800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1714300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1536300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1505700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1266400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2644600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1418900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2217200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2571500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3595300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3995800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4319300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4838300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3888900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2181700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2904900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2125100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3361600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2879600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1839100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1549200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1511900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1187400</v>
+      </c>
+      <c r="E96" s="3">
         <v>1085600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>995700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>877800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>825800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>729900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>885900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>836200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>862800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-777900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-744900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-716800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-655900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-582700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-493200</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,57 +4887,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-793700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>105300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>626600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>753100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1494300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>954500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-861800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-181000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-63200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>813900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-483400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-828100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-424800</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4723,8 +4971,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4741,55 +4989,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1277800</v>
+      </c>
+      <c r="E102" s="3">
         <v>3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-83300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>185500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-98800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>245600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>93300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-69600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>61400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>151900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>122400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-216700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>176300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>45900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>22300</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
